--- a/dataset/Part 6_3_3_ Acute Illness health seeking and expenditure tracking.xlsx
+++ b/dataset/Part 6_3_3_ Acute Illness health seeking and expenditure tracking.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B17E99-7FA7-4BDC-BB43-06B79CA88490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09842D9B-E1B0-49B4-A0F1-D2B0F0147165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4582" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4993" uniqueCount="1378">
   <si>
     <t>ID</t>
   </si>
@@ -3791,6 +3791,381 @@
   </si>
   <si>
     <t>f8adc194-db21-4c22-85c1-140798713348</t>
+  </si>
+  <si>
+    <t>547882f4-1a13-4c6d-95d8-b6d532cc488c</t>
+  </si>
+  <si>
+    <t>DOLOPAR</t>
+  </si>
+  <si>
+    <t>75b6324b-6147-44d2-8b3b-5307b0f9a18e</t>
+  </si>
+  <si>
+    <t>b8d17505-701a-46d9-aa63-74ca6534af19</t>
+  </si>
+  <si>
+    <t>28bb8c08-d832-4fb7-806c-cf99867618d7</t>
+  </si>
+  <si>
+    <t>feaa8f7a-74b0-4977-a01a-e7ef833a1a3a</t>
+  </si>
+  <si>
+    <t>3894641a-6548-48c2-b548-06478ae6eb9c</t>
+  </si>
+  <si>
+    <t>cd2c84ce-f139-46c4-b537-88a54c79ebb7</t>
+  </si>
+  <si>
+    <t>ca06fe52-d1f9-4180-8c7f-2ddf2bcc9e6d</t>
+  </si>
+  <si>
+    <t>उपचार गर्नु नपरेको</t>
+  </si>
+  <si>
+    <t>4184fda4-9895-472e-abb1-c0ebb01eb306</t>
+  </si>
+  <si>
+    <t>8b690fc2-a9c9-431a-88a5-f7f1b9df5ebd</t>
+  </si>
+  <si>
+    <t>c1899409-5d73-44e7-9ab2-06d40b2e9e37</t>
+  </si>
+  <si>
+    <t>1874f366-05a7-4729-bcdf-e6393999a71a</t>
+  </si>
+  <si>
+    <t>2aa80d0b-f465-4c89-980e-8e1abed20082</t>
+  </si>
+  <si>
+    <t>eb60c967-663c-4d52-82a3-09a2514fd604</t>
+  </si>
+  <si>
+    <t>fd2565a8-6754-497f-8d6a-2d1cea2dc191</t>
+  </si>
+  <si>
+    <t>8ee81f1f-953c-4fea-a9f4-ae42423f5135</t>
+  </si>
+  <si>
+    <t>7a80236f-5a2f-4181-b550-8289f6eb4eae</t>
+  </si>
+  <si>
+    <t>0114188a-e0a7-46ee-97ad-54c879be111f</t>
+  </si>
+  <si>
+    <t>0cd46ce2-b6f1-44ea-8289-926c5a818471</t>
+  </si>
+  <si>
+    <t>e1819ce6-e695-430d-acf4-976cd06d83fb</t>
+  </si>
+  <si>
+    <t>bd352ff8-7263-4d60-b580-22960a06dbe3</t>
+  </si>
+  <si>
+    <t>a2fdd2ab-9fed-40a2-ad0a-2add8c814dbc</t>
+  </si>
+  <si>
+    <t>38e316e0-eff7-4fdd-9971-133c46a26264</t>
+  </si>
+  <si>
+    <t>5faef702-6c2c-4439-ab05-9f5d0d69178c</t>
+  </si>
+  <si>
+    <t>2,96</t>
+  </si>
+  <si>
+    <t>UHA LAI MEDICINE KO NAME THAVAYENA UHA LEY BAHIRA PHARMACY MA KINNU BHAKO DABAI</t>
+  </si>
+  <si>
+    <t>NO CHECK UP</t>
+  </si>
+  <si>
+    <t>72bb4b2f-7752-4a7f-ae7f-1dcdf86aeb68</t>
+  </si>
+  <si>
+    <t>HE DOESN'T KNOW ABOUT THE MEDICINE NAME</t>
+  </si>
+  <si>
+    <t>2518c2ec-8b14-4e06-aead-2dc6f90801ab</t>
+  </si>
+  <si>
+    <t>GHAR MAI TATO PANI KHAYERA NIKO GARNU BHAYO</t>
+  </si>
+  <si>
+    <t>BIRKABIYAM,</t>
+  </si>
+  <si>
+    <t>58e607a3-c1ec-47fa-948c-3b0b58485817</t>
+  </si>
+  <si>
+    <t>NO CHECK UP GHAR MA TATO PANI KHARA BASNU BHAKO</t>
+  </si>
+  <si>
+    <t>STONIL, HYBRO DS , CEFIXIME , NILLATO SYRUP,METRONAZOLE, ESOFEST, ORS</t>
+  </si>
+  <si>
+    <t>a82bb8d4-c573-4c43-b290-add69a2bfd57</t>
+  </si>
+  <si>
+    <t>DON'T KNOW MEDICINE NAME, MEDICINE KO KAGAJ JALAKO</t>
+  </si>
+  <si>
+    <t>4401d441-2aee-427a-8987-3d7bcbf3cadf</t>
+  </si>
+  <si>
+    <t>7b525895-dc9f-4155-9541-08c7b97a9f47</t>
+  </si>
+  <si>
+    <t>90700619-91f6-4875-b179-4f3b10bf1d41</t>
+  </si>
+  <si>
+    <t>DABAI NAKHAYAKO</t>
+  </si>
+  <si>
+    <t>a7e74fef-193e-43e3-953d-3d70cd536ddd</t>
+  </si>
+  <si>
+    <t>4cf56919-f252-4fa6-9d68-d12e27df4aad</t>
+  </si>
+  <si>
+    <t>6faee429-6167-4b36-bdf5-b4b7c380f64f</t>
+  </si>
+  <si>
+    <t>AZIPAN-500,CETAMOL</t>
+  </si>
+  <si>
+    <t>d7921dd2-3110-4438-94bc-a9efd68de555</t>
+  </si>
+  <si>
+    <t>CALAZIN</t>
+  </si>
+  <si>
+    <t>0be13269-e4e0-41f9-ae55-0a886bc47ea3</t>
+  </si>
+  <si>
+    <t>ROCIN - B</t>
+  </si>
+  <si>
+    <t>ab66ea4e-8af2-4466-b2f4-ece73baaec6a</t>
+  </si>
+  <si>
+    <t>f8be633c-607b-4694-b130-b994ddbabcba</t>
+  </si>
+  <si>
+    <t>d5d3535e-355a-45df-bdd6-6cb6c51bd758</t>
+  </si>
+  <si>
+    <t>37d59658-0f94-4b20-b7ec-024169155e94</t>
+  </si>
+  <si>
+    <t>267d6b14-a607-4360-bf8c-3c0004c33211</t>
+  </si>
+  <si>
+    <t>c7e17a58-9733-4e00-90b4-88c04e802310</t>
+  </si>
+  <si>
+    <t>GHAM TAPERA NIKO HUNU BHO</t>
+  </si>
+  <si>
+    <t>65848f23-0751-4d34-b012-a25c71c79876</t>
+  </si>
+  <si>
+    <t>659bd5f2-7242-444d-8579-1ce7c6815a3f</t>
+  </si>
+  <si>
+    <t>7fa623a9-c7a4-43fc-9bac-59689d6d566d</t>
+  </si>
+  <si>
+    <t>D PAIN</t>
+  </si>
+  <si>
+    <t>c1dccd0c-a399-4bcf-8e3b-04ebd116b624</t>
+  </si>
+  <si>
+    <t>13cae60c-7a3f-49ff-99a3-b485b7ba7ef8</t>
+  </si>
+  <si>
+    <t>2d8d24e4-8ba7-47f9-970e-9e9d80bb8410</t>
+  </si>
+  <si>
+    <t>110dd625-5999-486e-83b8-59409c1192e2</t>
+  </si>
+  <si>
+    <t>9224f9d0-9c4d-425e-814d-44bf36554ba4</t>
+  </si>
+  <si>
+    <t>fca2cc28-c2c4-4e19-92f0-e39031cff05a</t>
+  </si>
+  <si>
+    <t>5363b112-6f24-4bca-995a-9e2afb015e00</t>
+  </si>
+  <si>
+    <t>0b4792ed-409e-4e04-9c66-aee486fe852e</t>
+  </si>
+  <si>
+    <t>bfdbd219-b25c-4560-b0b9-feb970d2aaa9</t>
+  </si>
+  <si>
+    <t>30c58655-91cc-4022-a25a-a684cb837fe9</t>
+  </si>
+  <si>
+    <t>9a91eb2e-2b56-498d-b056-30a62d3eb227</t>
+  </si>
+  <si>
+    <t>691de47d-a63d-42e6-8e7b-7642becbb54e</t>
+  </si>
+  <si>
+    <t>04ec46b3-66fa-4bd5-98a7-9da34c7ab94d</t>
+  </si>
+  <si>
+    <t>20b43056-c5bc-40ff-84cd-ced0d5b229aa</t>
+  </si>
+  <si>
+    <t>af150004-a4bc-42d2-9e64-4d5d1620387b</t>
+  </si>
+  <si>
+    <t>e8edf682-098e-4d6b-9111-a02e7c2b2f46</t>
+  </si>
+  <si>
+    <t>RESPONDENT TYPHOID BHAAEKO TARA MEDICINE KO NAAM LEKHNE THAUMA KHALI AAKO CHHA</t>
+  </si>
+  <si>
+    <t>844a9ce4-ecb5-4084-b8db-62d0effb5662</t>
+  </si>
+  <si>
+    <t>KUNAI AUSHADHI NA KHAKO</t>
+  </si>
+  <si>
+    <t>a2124962-4d70-4f9b-bc04-aeeddd2c560c</t>
+  </si>
+  <si>
+    <t>77e1f7e3-a784-4a4b-a072-5cdae15094f7</t>
+  </si>
+  <si>
+    <t>b319766a-14e9-4c2e-bc6a-038f03dce9d5</t>
+  </si>
+  <si>
+    <t>f834293f-5e57-49f7-8464-850c2aeed85f</t>
+  </si>
+  <si>
+    <t>dc1dcd77-e250-4c67-acbf-09a769b129cc</t>
+  </si>
+  <si>
+    <t>f4192c28-aea9-4c73-ba57-45ec56d598f2</t>
+  </si>
+  <si>
+    <t>3bd809ac-6aae-442c-9057-e349d18822e4</t>
+  </si>
+  <si>
+    <t>05ae2433-dbfc-4c46-88c2-7d585403c87e</t>
+  </si>
+  <si>
+    <t>f4bed1ae-bced-40a0-8894-5d38953ddca1</t>
+  </si>
+  <si>
+    <t>8c3a7ddd-cc8a-4e2d-9aaf-29f3bb4f6a20</t>
+  </si>
+  <si>
+    <t>832fc969-98fb-41a7-8c08-9605f61ab304</t>
+  </si>
+  <si>
+    <t>9e61fb4d-2e0c-41c1-b5dc-b32795b29db7</t>
+  </si>
+  <si>
+    <t>d2f28238-335d-43ec-a7f4-1361bdc3b0f0</t>
+  </si>
+  <si>
+    <t>783e9ad7-aad2-4b74-8557-0c6ff2934100</t>
+  </si>
+  <si>
+    <t>d7151a1b-9924-49f5-bc91-2db256954dbf</t>
+  </si>
+  <si>
+    <t>ea9c5908-3934-4c3a-a736-17e05c391f51</t>
+  </si>
+  <si>
+    <t>0f12f12d-5901-43af-8e73-bafd1baaa038</t>
+  </si>
+  <si>
+    <t>d9727735-d6d4-4988-ae4d-23dd221bc234</t>
+  </si>
+  <si>
+    <t>aa4dc137-e941-4837-ab35-eaf47bdd2a64</t>
+  </si>
+  <si>
+    <t>1891cd05-81fd-4622-97e7-eb79d8606aa0</t>
+  </si>
+  <si>
+    <t>e1d83c0c-0b51-426b-b82e-caa34c43ac00</t>
+  </si>
+  <si>
+    <t>669f0633-444a-408e-b356-a34e7bdc4aab</t>
+  </si>
+  <si>
+    <t>d4c36919-99a8-4c38-95f6-76781926663c</t>
+  </si>
+  <si>
+    <t>351a87aa-b390-4165-a691-9db071e252a6</t>
+  </si>
+  <si>
+    <t>668bbf66-5522-46de-9b80-d5d5c7e52551</t>
+  </si>
+  <si>
+    <t>71897eba-0dfe-4b42-a046-b9af9e8c2085</t>
+  </si>
+  <si>
+    <t>a06a42f0-adfd-4b4a-bcb3-1ca036d22cb5</t>
+  </si>
+  <si>
+    <t>0d33c29d-c199-4470-b682-1637a95fd13f</t>
+  </si>
+  <si>
+    <t>925e8fae-cdd4-4790-9cd0-d5d3ef6605f3</t>
+  </si>
+  <si>
+    <t>ab7832bd-87dc-48ec-a33b-4908fd5323a9</t>
+  </si>
+  <si>
+    <t>5ff8e763-c6b4-4f22-a85e-ad5a606ed179</t>
+  </si>
+  <si>
+    <t>988534d2-8995-4d21-ac04-7ad3d998d414</t>
+  </si>
+  <si>
+    <t>4bf9ec99-b91e-47fa-9b8c-a1407eee0f93</t>
+  </si>
+  <si>
+    <t>6b128734-48e4-4d59-b538-9c76a75585ef</t>
+  </si>
+  <si>
+    <t>7d0e35ea-15d2-4e80-8dd3-27dede3247de</t>
+  </si>
+  <si>
+    <t>7ee6c80c-6449-4a89-988f-543682d159d4</t>
+  </si>
+  <si>
+    <t>59e685cc-b565-4e8d-a702-f1c27376d3fe</t>
+  </si>
+  <si>
+    <t>278928d7-c501-4bd4-ab21-97071e3b55ac</t>
+  </si>
+  <si>
+    <t>fd7df7db-0410-4e73-a118-476b47e03b9c</t>
+  </si>
+  <si>
+    <t>1f5d0cb7-2344-4e3d-a3a7-8e67fdba9dce</t>
+  </si>
+  <si>
+    <t>c0b7c498-f905-45a7-acea-74c9b7a28f55</t>
+  </si>
+  <si>
+    <t>3bc597bb-7630-4121-abc1-20ac73e568a0</t>
+  </si>
+  <si>
+    <t>ede0c288-0712-4d2c-a57c-b885c0a9c06e</t>
+  </si>
+  <si>
+    <t>dce67f7d-3192-4b46-9822-85562317158a</t>
   </si>
 </sst>
 </file>
@@ -3836,9 +4211,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4143,7 +4519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1374"/>
+  <dimension ref="A1:AC1498"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -58426,6 +58802,4889 @@
         <v>46</v>
       </c>
     </row>
+    <row r="1375" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1375">
+        <v>11308</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C1375">
+        <v>3215</v>
+      </c>
+      <c r="D1375">
+        <v>31304</v>
+      </c>
+      <c r="E1375">
+        <v>4</v>
+      </c>
+      <c r="F1375">
+        <v>8</v>
+      </c>
+      <c r="G1375" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1375" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1375">
+        <v>25</v>
+      </c>
+      <c r="J1375">
+        <v>54759</v>
+      </c>
+      <c r="K1375">
+        <v>1</v>
+      </c>
+      <c r="AA1375" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AB1375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1376">
+        <v>11308</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C1376">
+        <v>3215</v>
+      </c>
+      <c r="D1376">
+        <v>31304</v>
+      </c>
+      <c r="E1376">
+        <v>4</v>
+      </c>
+      <c r="F1376">
+        <v>8</v>
+      </c>
+      <c r="G1376" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1376" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1376">
+        <v>25</v>
+      </c>
+      <c r="J1376">
+        <v>54762</v>
+      </c>
+      <c r="K1376">
+        <v>4</v>
+      </c>
+      <c r="AA1376" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AB1376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1377">
+        <v>11314</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C1377">
+        <v>3215</v>
+      </c>
+      <c r="D1377">
+        <v>31304</v>
+      </c>
+      <c r="E1377">
+        <v>4</v>
+      </c>
+      <c r="F1377">
+        <v>8</v>
+      </c>
+      <c r="G1377" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1377" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1377">
+        <v>26</v>
+      </c>
+      <c r="J1377">
+        <v>54780</v>
+      </c>
+      <c r="K1377">
+        <v>6</v>
+      </c>
+      <c r="AB1377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1378">
+        <v>11316</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C1378">
+        <v>3215</v>
+      </c>
+      <c r="D1378">
+        <v>31304</v>
+      </c>
+      <c r="E1378">
+        <v>4</v>
+      </c>
+      <c r="F1378">
+        <v>10</v>
+      </c>
+      <c r="G1378" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1378" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1378">
+        <v>26</v>
+      </c>
+      <c r="J1378">
+        <v>54787</v>
+      </c>
+      <c r="K1378">
+        <v>1</v>
+      </c>
+      <c r="AB1378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1379">
+        <v>11325</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1379">
+        <v>3215</v>
+      </c>
+      <c r="D1379">
+        <v>31304</v>
+      </c>
+      <c r="E1379">
+        <v>4</v>
+      </c>
+      <c r="F1379">
+        <v>18</v>
+      </c>
+      <c r="G1379" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1379" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1379">
+        <v>51</v>
+      </c>
+      <c r="J1379">
+        <v>54835</v>
+      </c>
+      <c r="K1379">
+        <v>3</v>
+      </c>
+      <c r="O1379">
+        <v>21</v>
+      </c>
+      <c r="AB1379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1380">
+        <v>11327</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C1380">
+        <v>3215</v>
+      </c>
+      <c r="D1380">
+        <v>31304</v>
+      </c>
+      <c r="E1380">
+        <v>4</v>
+      </c>
+      <c r="F1380">
+        <v>20</v>
+      </c>
+      <c r="G1380" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1380" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1380">
+        <v>51</v>
+      </c>
+      <c r="J1380">
+        <v>54843</v>
+      </c>
+      <c r="K1380">
+        <v>4</v>
+      </c>
+      <c r="AB1380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1381">
+        <v>11334</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C1381">
+        <v>3115</v>
+      </c>
+      <c r="D1381">
+        <v>31304</v>
+      </c>
+      <c r="E1381">
+        <v>4</v>
+      </c>
+      <c r="F1381">
+        <v>10</v>
+      </c>
+      <c r="G1381" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1381" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1381">
+        <v>53</v>
+      </c>
+      <c r="J1381">
+        <v>54872</v>
+      </c>
+      <c r="K1381">
+        <v>1</v>
+      </c>
+      <c r="AB1381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1382">
+        <v>11337</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C1382">
+        <v>3115</v>
+      </c>
+      <c r="D1382">
+        <v>31304</v>
+      </c>
+      <c r="E1382">
+        <v>4</v>
+      </c>
+      <c r="F1382">
+        <v>12</v>
+      </c>
+      <c r="G1382" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1382" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1382">
+        <v>51</v>
+      </c>
+      <c r="J1382">
+        <v>54887</v>
+      </c>
+      <c r="K1382">
+        <v>2</v>
+      </c>
+      <c r="O1382">
+        <v>21</v>
+      </c>
+      <c r="AB1382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1383">
+        <v>11340</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C1383">
+        <v>3115</v>
+      </c>
+      <c r="D1383">
+        <v>31304</v>
+      </c>
+      <c r="E1383">
+        <v>4</v>
+      </c>
+      <c r="F1383">
+        <v>16</v>
+      </c>
+      <c r="G1383" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1383" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1383">
+        <v>51</v>
+      </c>
+      <c r="J1383">
+        <v>54908</v>
+      </c>
+      <c r="K1383">
+        <v>3</v>
+      </c>
+      <c r="AB1383">
+        <v>96</v>
+      </c>
+      <c r="AC1383" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1384">
+        <v>11373</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C1384">
+        <v>1401</v>
+      </c>
+      <c r="D1384">
+        <v>10206</v>
+      </c>
+      <c r="E1384">
+        <v>9</v>
+      </c>
+      <c r="F1384">
+        <v>26</v>
+      </c>
+      <c r="G1384" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1384" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1384">
+        <v>91</v>
+      </c>
+      <c r="J1384">
+        <v>55044</v>
+      </c>
+      <c r="K1384">
+        <v>2</v>
+      </c>
+      <c r="V1384">
+        <v>91</v>
+      </c>
+      <c r="AB1384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1385">
+        <v>11373</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C1385">
+        <v>1401</v>
+      </c>
+      <c r="D1385">
+        <v>10206</v>
+      </c>
+      <c r="E1385">
+        <v>9</v>
+      </c>
+      <c r="F1385">
+        <v>26</v>
+      </c>
+      <c r="G1385" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1385" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1385">
+        <v>91</v>
+      </c>
+      <c r="J1385">
+        <v>55046</v>
+      </c>
+      <c r="K1385">
+        <v>4</v>
+      </c>
+      <c r="Y1385" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB1385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1386">
+        <v>11375</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F1386">
+        <v>28</v>
+      </c>
+      <c r="G1386" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1386" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1386">
+        <v>91</v>
+      </c>
+      <c r="J1386">
+        <v>55055</v>
+      </c>
+      <c r="K1386">
+        <v>4</v>
+      </c>
+      <c r="AA1386">
+        <v>142</v>
+      </c>
+      <c r="AB1386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1387">
+        <v>11384</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C1387">
+        <v>3608</v>
+      </c>
+      <c r="E1387">
+        <v>0</v>
+      </c>
+      <c r="F1387">
+        <v>37</v>
+      </c>
+      <c r="G1387" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1387" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1387">
+        <v>91</v>
+      </c>
+      <c r="J1387">
+        <v>55089</v>
+      </c>
+      <c r="K1387">
+        <v>3</v>
+      </c>
+      <c r="AA1387" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1388">
+        <v>11387</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C1388">
+        <v>3505</v>
+      </c>
+      <c r="E1388">
+        <v>0</v>
+      </c>
+      <c r="F1388">
+        <v>41</v>
+      </c>
+      <c r="G1388" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1388" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1388">
+        <v>91</v>
+      </c>
+      <c r="J1388">
+        <v>55102</v>
+      </c>
+      <c r="K1388">
+        <v>3</v>
+      </c>
+      <c r="AB1388">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1389">
+        <v>11388</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C1389">
+        <v>3605</v>
+      </c>
+      <c r="E1389">
+        <v>0</v>
+      </c>
+      <c r="F1389">
+        <v>42</v>
+      </c>
+      <c r="G1389" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1389" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1389">
+        <v>91</v>
+      </c>
+      <c r="J1389">
+        <v>55105</v>
+      </c>
+      <c r="K1389">
+        <v>3</v>
+      </c>
+      <c r="AA1389" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1390">
+        <v>11389</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1390">
+        <v>3604</v>
+      </c>
+      <c r="E1390">
+        <v>0</v>
+      </c>
+      <c r="F1390">
+        <v>43</v>
+      </c>
+      <c r="G1390" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1390" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1390">
+        <v>91</v>
+      </c>
+      <c r="J1390">
+        <v>55109</v>
+      </c>
+      <c r="K1390">
+        <v>3</v>
+      </c>
+      <c r="O1390">
+        <v>22</v>
+      </c>
+      <c r="AB1390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1391">
+        <v>11403</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C1391">
+        <v>3511</v>
+      </c>
+      <c r="D1391">
+        <v>30608</v>
+      </c>
+      <c r="E1391">
+        <v>4</v>
+      </c>
+      <c r="F1391">
+        <v>38</v>
+      </c>
+      <c r="G1391" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1391" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1391">
+        <v>93</v>
+      </c>
+      <c r="J1391">
+        <v>55166</v>
+      </c>
+      <c r="K1391">
+        <v>2</v>
+      </c>
+      <c r="AA1391">
+        <v>141</v>
+      </c>
+      <c r="AB1391">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1392">
+        <v>11454</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C1392">
+        <v>3520</v>
+      </c>
+      <c r="E1392">
+        <v>0</v>
+      </c>
+      <c r="F1392">
+        <v>25</v>
+      </c>
+      <c r="G1392" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1392" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1392">
+        <v>92</v>
+      </c>
+      <c r="J1392">
+        <v>55372</v>
+      </c>
+      <c r="K1392">
+        <v>1</v>
+      </c>
+      <c r="O1392" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1392">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1393">
+        <v>11483</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C1393">
+        <v>3519</v>
+      </c>
+      <c r="E1393">
+        <v>0</v>
+      </c>
+      <c r="F1393">
+        <v>27</v>
+      </c>
+      <c r="G1393" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1393" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1393">
+        <v>92</v>
+      </c>
+      <c r="J1393">
+        <v>55505</v>
+      </c>
+      <c r="K1393">
+        <v>1</v>
+      </c>
+      <c r="V1393">
+        <v>91</v>
+      </c>
+      <c r="AB1393">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1394">
+        <v>11495</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C1394">
+        <v>3615</v>
+      </c>
+      <c r="E1394">
+        <v>0</v>
+      </c>
+      <c r="F1394">
+        <v>50</v>
+      </c>
+      <c r="G1394" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1394" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1394">
+        <v>91</v>
+      </c>
+      <c r="J1394">
+        <v>55576</v>
+      </c>
+      <c r="K1394">
+        <v>1</v>
+      </c>
+      <c r="O1394">
+        <v>21</v>
+      </c>
+      <c r="AB1394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1395">
+        <v>11496</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C1395">
+        <v>3113</v>
+      </c>
+      <c r="D1395">
+        <v>31301</v>
+      </c>
+      <c r="E1395">
+        <v>7</v>
+      </c>
+      <c r="F1395">
+        <v>13</v>
+      </c>
+      <c r="G1395" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1395" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1395">
+        <v>26</v>
+      </c>
+      <c r="J1395">
+        <v>55584</v>
+      </c>
+      <c r="K1395">
+        <v>5</v>
+      </c>
+      <c r="Y1395">
+        <v>121</v>
+      </c>
+      <c r="AB1395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1396">
+        <v>11500</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C1396">
+        <v>3113</v>
+      </c>
+      <c r="D1396">
+        <v>31301</v>
+      </c>
+      <c r="E1396">
+        <v>7</v>
+      </c>
+      <c r="F1396">
+        <v>17</v>
+      </c>
+      <c r="G1396" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1396" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1396">
+        <v>26</v>
+      </c>
+      <c r="J1396">
+        <v>55606</v>
+      </c>
+      <c r="K1396">
+        <v>1</v>
+      </c>
+      <c r="AB1396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1397">
+        <v>11502</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C1397">
+        <v>3213</v>
+      </c>
+      <c r="D1397">
+        <v>31301</v>
+      </c>
+      <c r="E1397">
+        <v>7</v>
+      </c>
+      <c r="F1397">
+        <v>19</v>
+      </c>
+      <c r="G1397" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1397" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1397">
+        <v>26</v>
+      </c>
+      <c r="J1397">
+        <v>55613</v>
+      </c>
+      <c r="K1397">
+        <v>2</v>
+      </c>
+      <c r="AB1397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1398">
+        <v>11503</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C1398">
+        <v>3113</v>
+      </c>
+      <c r="E1398">
+        <v>7</v>
+      </c>
+      <c r="F1398">
+        <v>20</v>
+      </c>
+      <c r="G1398" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1398" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1398">
+        <v>26</v>
+      </c>
+      <c r="J1398">
+        <v>55618</v>
+      </c>
+      <c r="K1398">
+        <v>5</v>
+      </c>
+      <c r="AB1398">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1399">
+        <v>11505</v>
+      </c>
+      <c r="B1399" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C1399">
+        <v>3213</v>
+      </c>
+      <c r="D1399">
+        <v>31301</v>
+      </c>
+      <c r="E1399">
+        <v>7</v>
+      </c>
+      <c r="F1399">
+        <v>22</v>
+      </c>
+      <c r="G1399" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1399" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1399">
+        <v>26</v>
+      </c>
+      <c r="J1399">
+        <v>55631</v>
+      </c>
+      <c r="K1399">
+        <v>4</v>
+      </c>
+      <c r="AB1399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1400">
+        <v>11514</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C1400">
+        <v>7102</v>
+      </c>
+      <c r="D1400">
+        <v>70210</v>
+      </c>
+      <c r="E1400">
+        <v>4</v>
+      </c>
+      <c r="F1400">
+        <v>11</v>
+      </c>
+      <c r="G1400" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1400" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1400">
+        <v>72</v>
+      </c>
+      <c r="J1400">
+        <v>55675</v>
+      </c>
+      <c r="K1400">
+        <v>2</v>
+      </c>
+      <c r="O1400">
+        <v>21</v>
+      </c>
+      <c r="AB1400" t="s">
+        <v>1279</v>
+      </c>
+      <c r="AC1400" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1401">
+        <v>11514</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C1401">
+        <v>7102</v>
+      </c>
+      <c r="D1401">
+        <v>70210</v>
+      </c>
+      <c r="E1401">
+        <v>4</v>
+      </c>
+      <c r="F1401">
+        <v>11</v>
+      </c>
+      <c r="G1401" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1401" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1401">
+        <v>72</v>
+      </c>
+      <c r="J1401">
+        <v>55676</v>
+      </c>
+      <c r="K1401">
+        <v>3</v>
+      </c>
+      <c r="AB1401">
+        <v>96</v>
+      </c>
+      <c r="AC1401" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1402">
+        <v>11515</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C1402">
+        <v>7202</v>
+      </c>
+      <c r="D1402">
+        <v>70210</v>
+      </c>
+      <c r="E1402">
+        <v>6</v>
+      </c>
+      <c r="F1402">
+        <v>12</v>
+      </c>
+      <c r="G1402" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1402" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1402">
+        <v>72</v>
+      </c>
+      <c r="J1402">
+        <v>55682</v>
+      </c>
+      <c r="K1402">
+        <v>1</v>
+      </c>
+      <c r="AB1402">
+        <v>1</v>
+      </c>
+      <c r="AC1402" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1403">
+        <v>11520</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C1403">
+        <v>7202</v>
+      </c>
+      <c r="D1403">
+        <v>70210</v>
+      </c>
+      <c r="E1403">
+        <v>6</v>
+      </c>
+      <c r="F1403">
+        <v>17</v>
+      </c>
+      <c r="G1403" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1403" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1403">
+        <v>72</v>
+      </c>
+      <c r="J1403">
+        <v>55720</v>
+      </c>
+      <c r="K1403">
+        <v>1</v>
+      </c>
+      <c r="AB1403">
+        <v>96</v>
+      </c>
+      <c r="AC1403" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1404">
+        <v>11520</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C1404">
+        <v>7202</v>
+      </c>
+      <c r="D1404">
+        <v>70210</v>
+      </c>
+      <c r="E1404">
+        <v>6</v>
+      </c>
+      <c r="F1404">
+        <v>17</v>
+      </c>
+      <c r="G1404" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1404" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1404">
+        <v>72</v>
+      </c>
+      <c r="J1404">
+        <v>55722</v>
+      </c>
+      <c r="K1404">
+        <v>3</v>
+      </c>
+      <c r="AB1404">
+        <v>96</v>
+      </c>
+      <c r="AC1404" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1405">
+        <v>11520</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C1405">
+        <v>7202</v>
+      </c>
+      <c r="D1405">
+        <v>70210</v>
+      </c>
+      <c r="E1405">
+        <v>6</v>
+      </c>
+      <c r="F1405">
+        <v>17</v>
+      </c>
+      <c r="G1405" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1405" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1405">
+        <v>72</v>
+      </c>
+      <c r="J1405">
+        <v>55724</v>
+      </c>
+      <c r="K1405">
+        <v>5</v>
+      </c>
+      <c r="O1405">
+        <v>21</v>
+      </c>
+      <c r="AB1405" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC1405" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1406">
+        <v>11522</v>
+      </c>
+      <c r="B1406" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C1406">
+        <v>7102</v>
+      </c>
+      <c r="D1406">
+        <v>70210</v>
+      </c>
+      <c r="E1406">
+        <v>6</v>
+      </c>
+      <c r="F1406">
+        <v>19</v>
+      </c>
+      <c r="G1406" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1406" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1406">
+        <v>72</v>
+      </c>
+      <c r="J1406">
+        <v>55732</v>
+      </c>
+      <c r="K1406">
+        <v>3</v>
+      </c>
+      <c r="AB1406">
+        <v>96</v>
+      </c>
+      <c r="AC1406" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1407">
+        <v>11522</v>
+      </c>
+      <c r="B1407" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C1407">
+        <v>7102</v>
+      </c>
+      <c r="D1407">
+        <v>70210</v>
+      </c>
+      <c r="E1407">
+        <v>6</v>
+      </c>
+      <c r="F1407">
+        <v>19</v>
+      </c>
+      <c r="G1407" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1407" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1407">
+        <v>72</v>
+      </c>
+      <c r="J1407">
+        <v>55737</v>
+      </c>
+      <c r="K1407">
+        <v>8</v>
+      </c>
+      <c r="AA1407" t="s">
+        <v>1289</v>
+      </c>
+      <c r="AB1407" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1408">
+        <v>11523</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C1408">
+        <v>7202</v>
+      </c>
+      <c r="D1408">
+        <v>70210</v>
+      </c>
+      <c r="E1408">
+        <v>6</v>
+      </c>
+      <c r="F1408">
+        <v>20</v>
+      </c>
+      <c r="G1408" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1408" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1408">
+        <v>72</v>
+      </c>
+      <c r="J1408">
+        <v>55742</v>
+      </c>
+      <c r="K1408">
+        <v>5</v>
+      </c>
+      <c r="AA1408" t="s">
+        <v>1291</v>
+      </c>
+      <c r="AB1408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1409">
+        <v>11531</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1409">
+        <v>3113</v>
+      </c>
+      <c r="D1409">
+        <v>31301</v>
+      </c>
+      <c r="E1409">
+        <v>7</v>
+      </c>
+      <c r="F1409">
+        <v>22</v>
+      </c>
+      <c r="G1409" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1409" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1409">
+        <v>51</v>
+      </c>
+      <c r="J1409">
+        <v>55784</v>
+      </c>
+      <c r="K1409">
+        <v>1</v>
+      </c>
+      <c r="AB1409">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1410">
+        <v>11531</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1410">
+        <v>3113</v>
+      </c>
+      <c r="D1410">
+        <v>31301</v>
+      </c>
+      <c r="E1410">
+        <v>7</v>
+      </c>
+      <c r="F1410">
+        <v>22</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1410" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1410">
+        <v>51</v>
+      </c>
+      <c r="J1410">
+        <v>55786</v>
+      </c>
+      <c r="K1410">
+        <v>3</v>
+      </c>
+      <c r="AB1410">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1411">
+        <v>11534</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C1411">
+        <v>3113</v>
+      </c>
+      <c r="D1411">
+        <v>31301</v>
+      </c>
+      <c r="E1411">
+        <v>7</v>
+      </c>
+      <c r="F1411">
+        <v>25</v>
+      </c>
+      <c r="G1411" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1411" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1411">
+        <v>51</v>
+      </c>
+      <c r="J1411">
+        <v>55803</v>
+      </c>
+      <c r="K1411">
+        <v>3</v>
+      </c>
+      <c r="AB1411">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1412">
+        <v>11536</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C1412">
+        <v>3213</v>
+      </c>
+      <c r="D1412">
+        <v>31301</v>
+      </c>
+      <c r="E1412">
+        <v>7</v>
+      </c>
+      <c r="F1412">
+        <v>27</v>
+      </c>
+      <c r="G1412" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1412" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1412">
+        <v>51</v>
+      </c>
+      <c r="J1412">
+        <v>55808</v>
+      </c>
+      <c r="K1412">
+        <v>2</v>
+      </c>
+      <c r="AB1412">
+        <v>96</v>
+      </c>
+      <c r="AC1412" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1413">
+        <v>11540</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C1413">
+        <v>3213</v>
+      </c>
+      <c r="D1413">
+        <v>31301</v>
+      </c>
+      <c r="E1413">
+        <v>8</v>
+      </c>
+      <c r="F1413">
+        <v>31</v>
+      </c>
+      <c r="G1413" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1413" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1413">
+        <v>51</v>
+      </c>
+      <c r="J1413">
+        <v>55826</v>
+      </c>
+      <c r="K1413">
+        <v>3</v>
+      </c>
+      <c r="AB1413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1414">
+        <v>11548</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1414">
+        <v>3517</v>
+      </c>
+      <c r="D1414">
+        <v>30608</v>
+      </c>
+      <c r="E1414">
+        <v>31</v>
+      </c>
+      <c r="F1414">
+        <v>51</v>
+      </c>
+      <c r="G1414" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1414" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1414">
+        <v>93</v>
+      </c>
+      <c r="J1414">
+        <v>55858</v>
+      </c>
+      <c r="K1414">
+        <v>2</v>
+      </c>
+      <c r="O1414">
+        <v>21</v>
+      </c>
+      <c r="AB1414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1415">
+        <v>11549</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C1415">
+        <v>3113</v>
+      </c>
+      <c r="D1415">
+        <v>31301</v>
+      </c>
+      <c r="E1415">
+        <v>7</v>
+      </c>
+      <c r="F1415">
+        <v>1</v>
+      </c>
+      <c r="G1415" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1415" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1415">
+        <v>53</v>
+      </c>
+      <c r="J1415">
+        <v>55862</v>
+      </c>
+      <c r="K1415">
+        <v>1</v>
+      </c>
+      <c r="AB1415">
+        <v>2</v>
+      </c>
+      <c r="AC1415" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1416">
+        <v>11550</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C1416">
+        <v>3113</v>
+      </c>
+      <c r="D1416">
+        <v>31301</v>
+      </c>
+      <c r="E1416">
+        <v>7</v>
+      </c>
+      <c r="F1416">
+        <v>2</v>
+      </c>
+      <c r="G1416" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1416" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1416">
+        <v>53</v>
+      </c>
+      <c r="J1416">
+        <v>55869</v>
+      </c>
+      <c r="K1416">
+        <v>5</v>
+      </c>
+      <c r="AB1416">
+        <v>1</v>
+      </c>
+      <c r="AC1416" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1417">
+        <v>11557</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C1417">
+        <v>3213</v>
+      </c>
+      <c r="D1417">
+        <v>31301</v>
+      </c>
+      <c r="E1417">
+        <v>7</v>
+      </c>
+      <c r="F1417">
+        <v>4</v>
+      </c>
+      <c r="G1417" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1417" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1417">
+        <v>53</v>
+      </c>
+      <c r="J1417">
+        <v>55898</v>
+      </c>
+      <c r="K1417">
+        <v>2</v>
+      </c>
+      <c r="AB1417">
+        <v>1</v>
+      </c>
+      <c r="AC1417" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1418">
+        <v>11561</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C1418">
+        <v>3115</v>
+      </c>
+      <c r="D1418">
+        <v>31304</v>
+      </c>
+      <c r="E1418">
+        <v>4</v>
+      </c>
+      <c r="F1418">
+        <v>16</v>
+      </c>
+      <c r="G1418" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1418" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1418">
+        <v>51</v>
+      </c>
+      <c r="J1418">
+        <v>55918</v>
+      </c>
+      <c r="K1418">
+        <v>3</v>
+      </c>
+      <c r="AB1418">
+        <v>96</v>
+      </c>
+      <c r="AC1418" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1419">
+        <v>11564</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C1419">
+        <v>3115</v>
+      </c>
+      <c r="D1419">
+        <v>31304</v>
+      </c>
+      <c r="E1419">
+        <v>4</v>
+      </c>
+      <c r="F1419">
+        <v>12</v>
+      </c>
+      <c r="G1419" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1419" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1419">
+        <v>51</v>
+      </c>
+      <c r="J1419">
+        <v>55939</v>
+      </c>
+      <c r="K1419">
+        <v>2</v>
+      </c>
+      <c r="O1419">
+        <v>21</v>
+      </c>
+      <c r="AB1419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1420">
+        <v>11580</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C1420">
+        <v>3344</v>
+      </c>
+      <c r="D1420">
+        <v>30802</v>
+      </c>
+      <c r="E1420">
+        <v>14</v>
+      </c>
+      <c r="F1420">
+        <v>20</v>
+      </c>
+      <c r="G1420" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1420" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1420">
+        <v>56</v>
+      </c>
+      <c r="J1420">
+        <v>56022</v>
+      </c>
+      <c r="K1420">
+        <v>6</v>
+      </c>
+      <c r="AB1420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1421">
+        <v>11581</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C1421">
+        <v>3361</v>
+      </c>
+      <c r="D1421">
+        <v>30802</v>
+      </c>
+      <c r="E1421">
+        <v>22</v>
+      </c>
+      <c r="F1421">
+        <v>21</v>
+      </c>
+      <c r="G1421" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1421" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1421">
+        <v>56</v>
+      </c>
+      <c r="J1421">
+        <v>56023</v>
+      </c>
+      <c r="K1421">
+        <v>1</v>
+      </c>
+      <c r="O1421">
+        <v>21</v>
+      </c>
+      <c r="AB1421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1422">
+        <v>11587</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C1422">
+        <v>3516</v>
+      </c>
+      <c r="D1422">
+        <v>30703</v>
+      </c>
+      <c r="E1422">
+        <v>2</v>
+      </c>
+      <c r="F1422">
+        <v>39</v>
+      </c>
+      <c r="G1422" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1422" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1422">
+        <v>94</v>
+      </c>
+      <c r="J1422">
+        <v>56052</v>
+      </c>
+      <c r="K1422">
+        <v>4</v>
+      </c>
+      <c r="O1422" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1423">
+        <v>11593</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C1423">
+        <v>5110</v>
+      </c>
+      <c r="D1423">
+        <v>51106</v>
+      </c>
+      <c r="E1423">
+        <v>20</v>
+      </c>
+      <c r="F1423">
+        <v>34</v>
+      </c>
+      <c r="G1423" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1423" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1423">
+        <v>51</v>
+      </c>
+      <c r="J1423">
+        <v>56076</v>
+      </c>
+      <c r="K1423">
+        <v>1</v>
+      </c>
+      <c r="O1423">
+        <v>22</v>
+      </c>
+      <c r="AB1423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1424">
+        <v>11595</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1424">
+        <v>5110</v>
+      </c>
+      <c r="D1424">
+        <v>51106</v>
+      </c>
+      <c r="E1424">
+        <v>20</v>
+      </c>
+      <c r="F1424">
+        <v>42</v>
+      </c>
+      <c r="G1424" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1424" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1424">
+        <v>51</v>
+      </c>
+      <c r="J1424">
+        <v>56091</v>
+      </c>
+      <c r="K1424">
+        <v>6</v>
+      </c>
+      <c r="O1424">
+        <v>21</v>
+      </c>
+      <c r="AB1424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1425">
+        <v>11597</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1425">
+        <v>3362</v>
+      </c>
+      <c r="D1425">
+        <v>30802</v>
+      </c>
+      <c r="E1425">
+        <v>10</v>
+      </c>
+      <c r="F1425">
+        <v>23</v>
+      </c>
+      <c r="G1425" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1425" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1425">
+        <v>56</v>
+      </c>
+      <c r="J1425">
+        <v>56098</v>
+      </c>
+      <c r="K1425">
+        <v>1</v>
+      </c>
+      <c r="O1425">
+        <v>21</v>
+      </c>
+      <c r="AB1425">
+        <v>1</v>
+      </c>
+      <c r="AC1425" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1426">
+        <v>11598</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C1426">
+        <v>3518</v>
+      </c>
+      <c r="E1426">
+        <v>0</v>
+      </c>
+      <c r="F1426">
+        <v>54</v>
+      </c>
+      <c r="G1426" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1426" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1426">
+        <v>91</v>
+      </c>
+      <c r="J1426">
+        <v>56104</v>
+      </c>
+      <c r="K1426">
+        <v>3</v>
+      </c>
+      <c r="AA1426" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1427">
+        <v>11598</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C1427">
+        <v>3518</v>
+      </c>
+      <c r="E1427">
+        <v>0</v>
+      </c>
+      <c r="F1427">
+        <v>54</v>
+      </c>
+      <c r="G1427" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1427" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1427">
+        <v>91</v>
+      </c>
+      <c r="J1427">
+        <v>56105</v>
+      </c>
+      <c r="K1427">
+        <v>4</v>
+      </c>
+      <c r="V1427" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB1427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1428">
+        <v>11601</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1428">
+        <v>5110</v>
+      </c>
+      <c r="D1428">
+        <v>51106</v>
+      </c>
+      <c r="E1428">
+        <v>20</v>
+      </c>
+      <c r="F1428">
+        <v>30</v>
+      </c>
+      <c r="G1428" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1428" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1428">
+        <v>53</v>
+      </c>
+      <c r="J1428">
+        <v>56113</v>
+      </c>
+      <c r="K1428">
+        <v>1</v>
+      </c>
+      <c r="AB1428">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1429">
+        <v>11602</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C1429">
+        <v>5210</v>
+      </c>
+      <c r="D1429">
+        <v>51106</v>
+      </c>
+      <c r="E1429">
+        <v>20</v>
+      </c>
+      <c r="F1429">
+        <v>31</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1429" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1429">
+        <v>53</v>
+      </c>
+      <c r="J1429">
+        <v>56117</v>
+      </c>
+      <c r="K1429">
+        <v>1</v>
+      </c>
+      <c r="Y1429">
+        <v>121</v>
+      </c>
+      <c r="AB1429">
+        <v>1</v>
+      </c>
+      <c r="AC1429" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1430">
+        <v>11604</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1430">
+        <v>5210</v>
+      </c>
+      <c r="D1430">
+        <v>51106</v>
+      </c>
+      <c r="E1430">
+        <v>20</v>
+      </c>
+      <c r="F1430">
+        <v>33</v>
+      </c>
+      <c r="G1430" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1430" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1430">
+        <v>53</v>
+      </c>
+      <c r="J1430">
+        <v>56129</v>
+      </c>
+      <c r="K1430">
+        <v>4</v>
+      </c>
+      <c r="O1430">
+        <v>21</v>
+      </c>
+      <c r="AB1430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1431">
+        <v>11605</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C1431">
+        <v>5110</v>
+      </c>
+      <c r="D1431">
+        <v>51106</v>
+      </c>
+      <c r="E1431">
+        <v>20</v>
+      </c>
+      <c r="F1431">
+        <v>34</v>
+      </c>
+      <c r="G1431" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1431" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1431">
+        <v>53</v>
+      </c>
+      <c r="J1431">
+        <v>56134</v>
+      </c>
+      <c r="K1431">
+        <v>4</v>
+      </c>
+      <c r="O1431">
+        <v>21</v>
+      </c>
+      <c r="AB1431">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1432">
+        <v>11606</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C1432">
+        <v>5110</v>
+      </c>
+      <c r="D1432">
+        <v>51106</v>
+      </c>
+      <c r="E1432">
+        <v>20</v>
+      </c>
+      <c r="F1432">
+        <v>35</v>
+      </c>
+      <c r="G1432" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1432" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1432">
+        <v>53</v>
+      </c>
+      <c r="J1432">
+        <v>56137</v>
+      </c>
+      <c r="K1432">
+        <v>1</v>
+      </c>
+      <c r="O1432">
+        <v>21</v>
+      </c>
+      <c r="AB1432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1433">
+        <v>11607</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C1433">
+        <v>5210</v>
+      </c>
+      <c r="D1433">
+        <v>51106</v>
+      </c>
+      <c r="E1433">
+        <v>20</v>
+      </c>
+      <c r="F1433">
+        <v>36</v>
+      </c>
+      <c r="G1433" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1433" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1433">
+        <v>53</v>
+      </c>
+      <c r="J1433">
+        <v>56145</v>
+      </c>
+      <c r="K1433">
+        <v>2</v>
+      </c>
+      <c r="O1433">
+        <v>21</v>
+      </c>
+      <c r="AB1433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1434">
+        <v>11607</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C1434">
+        <v>5210</v>
+      </c>
+      <c r="D1434">
+        <v>51106</v>
+      </c>
+      <c r="E1434">
+        <v>20</v>
+      </c>
+      <c r="F1434">
+        <v>36</v>
+      </c>
+      <c r="G1434" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1434" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1434">
+        <v>53</v>
+      </c>
+      <c r="J1434">
+        <v>56146</v>
+      </c>
+      <c r="K1434">
+        <v>3</v>
+      </c>
+      <c r="O1434">
+        <v>21</v>
+      </c>
+      <c r="AB1434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1435">
+        <v>11607</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C1435">
+        <v>5210</v>
+      </c>
+      <c r="D1435">
+        <v>51106</v>
+      </c>
+      <c r="E1435">
+        <v>20</v>
+      </c>
+      <c r="F1435">
+        <v>36</v>
+      </c>
+      <c r="G1435" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1435" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1435">
+        <v>53</v>
+      </c>
+      <c r="J1435">
+        <v>56148</v>
+      </c>
+      <c r="K1435">
+        <v>5</v>
+      </c>
+      <c r="U1435">
+        <v>81</v>
+      </c>
+      <c r="W1435">
+        <v>101</v>
+      </c>
+      <c r="AB1435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1436">
+        <v>11612</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C1436">
+        <v>5210</v>
+      </c>
+      <c r="D1436">
+        <v>51106</v>
+      </c>
+      <c r="E1436">
+        <v>20</v>
+      </c>
+      <c r="F1436">
+        <v>41</v>
+      </c>
+      <c r="G1436" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1436" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1436">
+        <v>53</v>
+      </c>
+      <c r="J1436">
+        <v>56173</v>
+      </c>
+      <c r="K1436">
+        <v>1</v>
+      </c>
+      <c r="O1436">
+        <v>21</v>
+      </c>
+      <c r="AB1436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1437">
+        <v>11613</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C1437">
+        <v>5210</v>
+      </c>
+      <c r="D1437">
+        <v>51106</v>
+      </c>
+      <c r="E1437">
+        <v>20</v>
+      </c>
+      <c r="F1437">
+        <v>42</v>
+      </c>
+      <c r="G1437" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1437" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1437">
+        <v>53</v>
+      </c>
+      <c r="J1437">
+        <v>56177</v>
+      </c>
+      <c r="K1437">
+        <v>3</v>
+      </c>
+      <c r="AB1437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1438">
+        <v>11613</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C1438">
+        <v>5210</v>
+      </c>
+      <c r="D1438">
+        <v>51106</v>
+      </c>
+      <c r="E1438">
+        <v>20</v>
+      </c>
+      <c r="F1438">
+        <v>42</v>
+      </c>
+      <c r="G1438" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1438" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1438">
+        <v>53</v>
+      </c>
+      <c r="J1438">
+        <v>56178</v>
+      </c>
+      <c r="K1438">
+        <v>4</v>
+      </c>
+      <c r="AB1438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1439">
+        <v>11633</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C1439">
+        <v>7102</v>
+      </c>
+      <c r="D1439">
+        <v>70210</v>
+      </c>
+      <c r="E1439">
+        <v>6</v>
+      </c>
+      <c r="F1439">
+        <v>7</v>
+      </c>
+      <c r="G1439" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1439" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1439">
+        <v>74</v>
+      </c>
+      <c r="J1439">
+        <v>56262</v>
+      </c>
+      <c r="K1439">
+        <v>4</v>
+      </c>
+      <c r="AB1439">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1440">
+        <v>11634</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C1440">
+        <v>7202</v>
+      </c>
+      <c r="D1440">
+        <v>70210</v>
+      </c>
+      <c r="E1440">
+        <v>6</v>
+      </c>
+      <c r="F1440">
+        <v>10</v>
+      </c>
+      <c r="G1440" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1440" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1440">
+        <v>74</v>
+      </c>
+      <c r="J1440">
+        <v>56267</v>
+      </c>
+      <c r="K1440">
+        <v>4</v>
+      </c>
+      <c r="AB1440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1441">
+        <v>11662</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C1441">
+        <v>3362</v>
+      </c>
+      <c r="D1441">
+        <v>30802</v>
+      </c>
+      <c r="E1441">
+        <v>10</v>
+      </c>
+      <c r="F1441">
+        <v>20</v>
+      </c>
+      <c r="G1441" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1441" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1441">
+        <v>58</v>
+      </c>
+      <c r="J1441">
+        <v>56369</v>
+      </c>
+      <c r="K1441">
+        <v>2</v>
+      </c>
+      <c r="AB1441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1442">
+        <v>11668</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C1442">
+        <v>7202</v>
+      </c>
+      <c r="D1442">
+        <v>70210</v>
+      </c>
+      <c r="E1442">
+        <v>6</v>
+      </c>
+      <c r="F1442">
+        <v>12</v>
+      </c>
+      <c r="G1442" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1442" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1442">
+        <v>74</v>
+      </c>
+      <c r="J1442">
+        <v>56399</v>
+      </c>
+      <c r="K1442">
+        <v>6</v>
+      </c>
+      <c r="AB1442">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1443">
+        <v>11673</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C1443">
+        <v>7102</v>
+      </c>
+      <c r="D1443">
+        <v>70210</v>
+      </c>
+      <c r="E1443">
+        <v>4</v>
+      </c>
+      <c r="F1443">
+        <v>12</v>
+      </c>
+      <c r="G1443" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1443" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1443">
+        <v>73</v>
+      </c>
+      <c r="J1443">
+        <v>56422</v>
+      </c>
+      <c r="K1443">
+        <v>3</v>
+      </c>
+      <c r="AB1443">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1444">
+        <v>11674</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C1444">
+        <v>7202</v>
+      </c>
+      <c r="D1444">
+        <v>70210</v>
+      </c>
+      <c r="E1444">
+        <v>4</v>
+      </c>
+      <c r="F1444">
+        <v>13</v>
+      </c>
+      <c r="G1444" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1444" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1444">
+        <v>73</v>
+      </c>
+      <c r="J1444">
+        <v>56429</v>
+      </c>
+      <c r="K1444">
+        <v>5</v>
+      </c>
+      <c r="AB1444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1445">
+        <v>11683</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C1445">
+        <v>5210</v>
+      </c>
+      <c r="D1445">
+        <v>51106</v>
+      </c>
+      <c r="E1445">
+        <v>20</v>
+      </c>
+      <c r="F1445">
+        <v>38</v>
+      </c>
+      <c r="G1445" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1445" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1445">
+        <v>51</v>
+      </c>
+      <c r="J1445">
+        <v>56474</v>
+      </c>
+      <c r="K1445">
+        <v>1</v>
+      </c>
+      <c r="O1445">
+        <v>21</v>
+      </c>
+      <c r="AB1445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1446">
+        <v>11685</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C1446">
+        <v>3630</v>
+      </c>
+      <c r="E1446">
+        <v>0</v>
+      </c>
+      <c r="F1446">
+        <v>22</v>
+      </c>
+      <c r="G1446" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1446" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1446">
+        <v>58</v>
+      </c>
+      <c r="J1446">
+        <v>56488</v>
+      </c>
+      <c r="K1446">
+        <v>2</v>
+      </c>
+      <c r="O1446">
+        <v>21</v>
+      </c>
+      <c r="AB1446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1447">
+        <v>11689</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C1447">
+        <v>3618</v>
+      </c>
+      <c r="D1447">
+        <v>30610</v>
+      </c>
+      <c r="E1447">
+        <v>7</v>
+      </c>
+      <c r="F1447">
+        <v>56</v>
+      </c>
+      <c r="G1447" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1447" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1447">
+        <v>94</v>
+      </c>
+      <c r="J1447">
+        <v>56502</v>
+      </c>
+      <c r="K1447">
+        <v>1</v>
+      </c>
+      <c r="O1447" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB1447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1448">
+        <v>11692</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1448">
+        <v>5109</v>
+      </c>
+      <c r="D1448">
+        <v>51105</v>
+      </c>
+      <c r="E1448">
+        <v>4</v>
+      </c>
+      <c r="F1448">
+        <v>15</v>
+      </c>
+      <c r="G1448" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1448" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1448">
+        <v>61</v>
+      </c>
+      <c r="J1448">
+        <v>56518</v>
+      </c>
+      <c r="K1448">
+        <v>1</v>
+      </c>
+      <c r="AB1448">
+        <v>4</v>
+      </c>
+      <c r="AC1448" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1449">
+        <v>11705</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C1449">
+        <v>3359</v>
+      </c>
+      <c r="D1449">
+        <v>30802</v>
+      </c>
+      <c r="E1449">
+        <v>13</v>
+      </c>
+      <c r="F1449">
+        <v>7</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1449" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1449">
+        <v>55</v>
+      </c>
+      <c r="J1449">
+        <v>56586</v>
+      </c>
+      <c r="K1449">
+        <v>2</v>
+      </c>
+      <c r="AB1449">
+        <v>96</v>
+      </c>
+      <c r="AC1449" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1450">
+        <v>11712</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C1450">
+        <v>3518</v>
+      </c>
+      <c r="D1450">
+        <v>30610</v>
+      </c>
+      <c r="E1450">
+        <v>7</v>
+      </c>
+      <c r="F1450">
+        <v>57</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1450" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1450">
+        <v>93</v>
+      </c>
+      <c r="J1450">
+        <v>56612</v>
+      </c>
+      <c r="K1450">
+        <v>2</v>
+      </c>
+      <c r="AA1450">
+        <v>141</v>
+      </c>
+      <c r="AB1450">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1451">
+        <v>11713</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C1451">
+        <v>3518</v>
+      </c>
+      <c r="D1451">
+        <v>30610</v>
+      </c>
+      <c r="E1451">
+        <v>7</v>
+      </c>
+      <c r="F1451">
+        <v>58</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1451" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1451">
+        <v>93</v>
+      </c>
+      <c r="J1451">
+        <v>56616</v>
+      </c>
+      <c r="K1451">
+        <v>1</v>
+      </c>
+      <c r="AA1451">
+        <v>141</v>
+      </c>
+      <c r="AB1451">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1452">
+        <v>11714</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C1452">
+        <v>3618</v>
+      </c>
+      <c r="D1452">
+        <v>30610</v>
+      </c>
+      <c r="E1452">
+        <v>7</v>
+      </c>
+      <c r="F1452">
+        <v>59</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1452" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1452">
+        <v>93</v>
+      </c>
+      <c r="J1452">
+        <v>56620</v>
+      </c>
+      <c r="K1452">
+        <v>2</v>
+      </c>
+      <c r="AB1452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1453">
+        <v>11725</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1453">
+        <v>3576</v>
+      </c>
+      <c r="E1453">
+        <v>0</v>
+      </c>
+      <c r="F1453">
+        <v>57</v>
+      </c>
+      <c r="G1453" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1453" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1453">
+        <v>91</v>
+      </c>
+      <c r="J1453">
+        <v>56671</v>
+      </c>
+      <c r="K1453">
+        <v>4</v>
+      </c>
+      <c r="AA1453" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1454">
+        <v>11735</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C1454">
+        <v>1207</v>
+      </c>
+      <c r="D1454">
+        <v>11102</v>
+      </c>
+      <c r="E1454">
+        <v>3</v>
+      </c>
+      <c r="F1454">
+        <v>34</v>
+      </c>
+      <c r="G1454" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1454" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1454">
+        <v>11</v>
+      </c>
+      <c r="J1454">
+        <v>56718</v>
+      </c>
+      <c r="K1454">
+        <v>2</v>
+      </c>
+      <c r="U1454">
+        <v>81</v>
+      </c>
+      <c r="AB1454">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1455">
+        <v>11736</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C1455">
+        <v>1207</v>
+      </c>
+      <c r="D1455">
+        <v>11102</v>
+      </c>
+      <c r="E1455">
+        <v>3</v>
+      </c>
+      <c r="F1455">
+        <v>35</v>
+      </c>
+      <c r="G1455" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1455" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1455">
+        <v>11</v>
+      </c>
+      <c r="J1455">
+        <v>56723</v>
+      </c>
+      <c r="K1455">
+        <v>2</v>
+      </c>
+      <c r="AB1455">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1456">
+        <v>11737</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C1456">
+        <v>1207</v>
+      </c>
+      <c r="D1456">
+        <v>11102</v>
+      </c>
+      <c r="E1456">
+        <v>3</v>
+      </c>
+      <c r="F1456">
+        <v>36</v>
+      </c>
+      <c r="G1456" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1456" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1456">
+        <v>11</v>
+      </c>
+      <c r="J1456">
+        <v>56729</v>
+      </c>
+      <c r="K1456">
+        <v>3</v>
+      </c>
+      <c r="U1456">
+        <v>82</v>
+      </c>
+      <c r="AB1456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1457">
+        <v>11754</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C1457">
+        <v>3676</v>
+      </c>
+      <c r="E1457">
+        <v>28</v>
+      </c>
+      <c r="F1457">
+        <v>60</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1457" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1457">
+        <v>91</v>
+      </c>
+      <c r="J1457">
+        <v>56812</v>
+      </c>
+      <c r="K1457">
+        <v>2</v>
+      </c>
+      <c r="U1457">
+        <v>81</v>
+      </c>
+      <c r="AB1457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1458">
+        <v>11757</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C1458">
+        <v>3676</v>
+      </c>
+      <c r="E1458">
+        <v>0</v>
+      </c>
+      <c r="F1458">
+        <v>61</v>
+      </c>
+      <c r="G1458" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1458" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1458">
+        <v>91</v>
+      </c>
+      <c r="J1458">
+        <v>56825</v>
+      </c>
+      <c r="K1458">
+        <v>1</v>
+      </c>
+      <c r="O1458">
+        <v>21</v>
+      </c>
+      <c r="AB1458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1459">
+        <v>11760</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C1459">
+        <v>3541</v>
+      </c>
+      <c r="E1459">
+        <v>0</v>
+      </c>
+      <c r="F1459">
+        <v>24</v>
+      </c>
+      <c r="G1459" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1459" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1459">
+        <v>58</v>
+      </c>
+      <c r="J1459">
+        <v>56840</v>
+      </c>
+      <c r="K1459">
+        <v>2</v>
+      </c>
+      <c r="AB1459">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1460">
+        <v>11787</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C1460">
+        <v>1102</v>
+      </c>
+      <c r="D1460">
+        <v>10304</v>
+      </c>
+      <c r="E1460">
+        <v>4</v>
+      </c>
+      <c r="F1460">
+        <v>38</v>
+      </c>
+      <c r="G1460" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1460" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1460">
+        <v>13</v>
+      </c>
+      <c r="J1460">
+        <v>57013</v>
+      </c>
+      <c r="K1460">
+        <v>3</v>
+      </c>
+      <c r="O1460">
+        <v>21</v>
+      </c>
+      <c r="AB1460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1461">
+        <v>11809</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C1461">
+        <v>3613</v>
+      </c>
+      <c r="E1461">
+        <v>0</v>
+      </c>
+      <c r="F1461">
+        <v>44</v>
+      </c>
+      <c r="G1461" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1461" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1461">
+        <v>91</v>
+      </c>
+      <c r="J1461">
+        <v>57131</v>
+      </c>
+      <c r="K1461">
+        <v>3</v>
+      </c>
+      <c r="O1461" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1462">
+        <v>11826</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C1462">
+        <v>3623</v>
+      </c>
+      <c r="D1462">
+        <v>30608</v>
+      </c>
+      <c r="E1462">
+        <v>14</v>
+      </c>
+      <c r="F1462">
+        <v>65</v>
+      </c>
+      <c r="G1462" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1462" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1462">
+        <v>93</v>
+      </c>
+      <c r="J1462">
+        <v>57231</v>
+      </c>
+      <c r="K1462">
+        <v>1</v>
+      </c>
+      <c r="O1462">
+        <v>21</v>
+      </c>
+      <c r="AB1462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1463">
+        <v>11868</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1463">
+        <v>3525</v>
+      </c>
+      <c r="E1463">
+        <v>0</v>
+      </c>
+      <c r="F1463">
+        <v>51</v>
+      </c>
+      <c r="G1463" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1463" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1463">
+        <v>92</v>
+      </c>
+      <c r="J1463">
+        <v>57494</v>
+      </c>
+      <c r="K1463">
+        <v>1</v>
+      </c>
+      <c r="O1463" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1463">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1464">
+        <v>11869</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C1464">
+        <v>3525</v>
+      </c>
+      <c r="E1464">
+        <v>0</v>
+      </c>
+      <c r="F1464">
+        <v>50</v>
+      </c>
+      <c r="G1464" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1464" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1464">
+        <v>92</v>
+      </c>
+      <c r="J1464">
+        <v>57499</v>
+      </c>
+      <c r="K1464">
+        <v>1</v>
+      </c>
+      <c r="AB1464">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1465">
+        <v>11870</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C1465">
+        <v>3621</v>
+      </c>
+      <c r="E1465">
+        <v>0</v>
+      </c>
+      <c r="F1465">
+        <v>52</v>
+      </c>
+      <c r="G1465" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1465" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1465">
+        <v>92</v>
+      </c>
+      <c r="J1465">
+        <v>57501</v>
+      </c>
+      <c r="K1465">
+        <v>1</v>
+      </c>
+      <c r="AB1465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1466">
+        <v>11872</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C1466">
+        <v>3622</v>
+      </c>
+      <c r="E1466">
+        <v>0</v>
+      </c>
+      <c r="F1466">
+        <v>54</v>
+      </c>
+      <c r="G1466" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1466" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1466">
+        <v>92</v>
+      </c>
+      <c r="J1466">
+        <v>57508</v>
+      </c>
+      <c r="K1466">
+        <v>1</v>
+      </c>
+      <c r="AB1466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1467">
+        <v>11875</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1467">
+        <v>3577</v>
+      </c>
+      <c r="E1467">
+        <v>0</v>
+      </c>
+      <c r="F1467">
+        <v>59</v>
+      </c>
+      <c r="G1467" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1467" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1467">
+        <v>92</v>
+      </c>
+      <c r="J1467">
+        <v>57525</v>
+      </c>
+      <c r="K1467">
+        <v>1</v>
+      </c>
+      <c r="AB1467">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1468">
+        <v>11883</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C1468">
+        <v>4207</v>
+      </c>
+      <c r="D1468">
+        <v>40806</v>
+      </c>
+      <c r="E1468">
+        <v>14</v>
+      </c>
+      <c r="F1468">
+        <v>24</v>
+      </c>
+      <c r="G1468" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1468" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1468">
+        <v>26</v>
+      </c>
+      <c r="J1468">
+        <v>57571</v>
+      </c>
+      <c r="K1468">
+        <v>5</v>
+      </c>
+      <c r="O1468">
+        <v>21</v>
+      </c>
+      <c r="AB1468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1469">
+        <v>11886</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C1469">
+        <v>4107</v>
+      </c>
+      <c r="D1469">
+        <v>40806</v>
+      </c>
+      <c r="E1469">
+        <v>14</v>
+      </c>
+      <c r="F1469">
+        <v>27</v>
+      </c>
+      <c r="G1469" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1469" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1469">
+        <v>26</v>
+      </c>
+      <c r="J1469">
+        <v>57588</v>
+      </c>
+      <c r="K1469">
+        <v>1</v>
+      </c>
+      <c r="AB1469">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1470">
+        <v>11886</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C1470">
+        <v>4107</v>
+      </c>
+      <c r="D1470">
+        <v>40806</v>
+      </c>
+      <c r="E1470">
+        <v>14</v>
+      </c>
+      <c r="F1470">
+        <v>27</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1470" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1470">
+        <v>26</v>
+      </c>
+      <c r="J1470">
+        <v>57590</v>
+      </c>
+      <c r="K1470">
+        <v>3</v>
+      </c>
+      <c r="AB1470" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1471">
+        <v>11886</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C1471">
+        <v>4107</v>
+      </c>
+      <c r="D1471">
+        <v>40806</v>
+      </c>
+      <c r="E1471">
+        <v>14</v>
+      </c>
+      <c r="F1471">
+        <v>27</v>
+      </c>
+      <c r="G1471" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1471" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1471">
+        <v>26</v>
+      </c>
+      <c r="J1471">
+        <v>57591</v>
+      </c>
+      <c r="K1471">
+        <v>4</v>
+      </c>
+      <c r="AB1471">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1472">
+        <v>11887</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C1472">
+        <v>4107</v>
+      </c>
+      <c r="D1472">
+        <v>40806</v>
+      </c>
+      <c r="E1472">
+        <v>14</v>
+      </c>
+      <c r="F1472">
+        <v>28</v>
+      </c>
+      <c r="G1472" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1472" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1472">
+        <v>26</v>
+      </c>
+      <c r="J1472">
+        <v>57597</v>
+      </c>
+      <c r="K1472">
+        <v>4</v>
+      </c>
+      <c r="AB1472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1473">
+        <v>11896</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C1473">
+        <v>4107</v>
+      </c>
+      <c r="E1473">
+        <v>14</v>
+      </c>
+      <c r="F1473">
+        <v>29</v>
+      </c>
+      <c r="G1473" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1473" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1473">
+        <v>26</v>
+      </c>
+      <c r="J1473">
+        <v>57646</v>
+      </c>
+      <c r="K1473">
+        <v>2</v>
+      </c>
+      <c r="AB1473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1474">
+        <v>11896</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C1474">
+        <v>4107</v>
+      </c>
+      <c r="E1474">
+        <v>14</v>
+      </c>
+      <c r="F1474">
+        <v>29</v>
+      </c>
+      <c r="G1474" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1474" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1474">
+        <v>26</v>
+      </c>
+      <c r="J1474">
+        <v>57654</v>
+      </c>
+      <c r="K1474">
+        <v>10</v>
+      </c>
+      <c r="AB1474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1475">
+        <v>11898</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C1475">
+        <v>4107</v>
+      </c>
+      <c r="D1475">
+        <v>40806</v>
+      </c>
+      <c r="E1475">
+        <v>14</v>
+      </c>
+      <c r="F1475">
+        <v>31</v>
+      </c>
+      <c r="G1475" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1475" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1475">
+        <v>26</v>
+      </c>
+      <c r="J1475">
+        <v>57663</v>
+      </c>
+      <c r="K1475">
+        <v>1</v>
+      </c>
+      <c r="AB1475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1476">
+        <v>11902</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1476">
+        <v>4107</v>
+      </c>
+      <c r="D1476">
+        <v>40806</v>
+      </c>
+      <c r="E1476">
+        <v>14</v>
+      </c>
+      <c r="F1476">
+        <v>35</v>
+      </c>
+      <c r="G1476" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1476" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1476">
+        <v>26</v>
+      </c>
+      <c r="J1476">
+        <v>57683</v>
+      </c>
+      <c r="K1476">
+        <v>2</v>
+      </c>
+      <c r="O1476">
+        <v>21</v>
+      </c>
+      <c r="AB1476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1477">
+        <v>11908</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C1477">
+        <v>7202</v>
+      </c>
+      <c r="D1477">
+        <v>70210</v>
+      </c>
+      <c r="E1477">
+        <v>6</v>
+      </c>
+      <c r="F1477">
+        <v>12</v>
+      </c>
+      <c r="G1477" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1477" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1477">
+        <v>71</v>
+      </c>
+      <c r="J1477">
+        <v>57713</v>
+      </c>
+      <c r="K1477">
+        <v>6</v>
+      </c>
+      <c r="O1477">
+        <v>21</v>
+      </c>
+      <c r="AB1477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1478">
+        <v>11909</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1478">
+        <v>7102</v>
+      </c>
+      <c r="D1478">
+        <v>70210</v>
+      </c>
+      <c r="E1478">
+        <v>6</v>
+      </c>
+      <c r="F1478">
+        <v>13</v>
+      </c>
+      <c r="G1478" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1478" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1478">
+        <v>71</v>
+      </c>
+      <c r="J1478">
+        <v>57719</v>
+      </c>
+      <c r="K1478">
+        <v>3</v>
+      </c>
+      <c r="AB1478">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1479">
+        <v>11910</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C1479">
+        <v>7202</v>
+      </c>
+      <c r="D1479">
+        <v>70210</v>
+      </c>
+      <c r="E1479">
+        <v>6</v>
+      </c>
+      <c r="F1479">
+        <v>14</v>
+      </c>
+      <c r="G1479" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1479" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1479">
+        <v>71</v>
+      </c>
+      <c r="J1479">
+        <v>57723</v>
+      </c>
+      <c r="K1479">
+        <v>4</v>
+      </c>
+      <c r="O1479">
+        <v>21</v>
+      </c>
+      <c r="AB1479">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1480">
+        <v>11911</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C1480">
+        <v>7102</v>
+      </c>
+      <c r="D1480">
+        <v>70210</v>
+      </c>
+      <c r="E1480">
+        <v>6</v>
+      </c>
+      <c r="F1480">
+        <v>15</v>
+      </c>
+      <c r="G1480" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1480" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1480">
+        <v>71</v>
+      </c>
+      <c r="J1480">
+        <v>57724</v>
+      </c>
+      <c r="K1480">
+        <v>1</v>
+      </c>
+      <c r="AB1480">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1481">
+        <v>11912</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C1481">
+        <v>7201</v>
+      </c>
+      <c r="D1481">
+        <v>70103</v>
+      </c>
+      <c r="E1481">
+        <v>6</v>
+      </c>
+      <c r="F1481">
+        <v>16</v>
+      </c>
+      <c r="G1481" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1481" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1481">
+        <v>71</v>
+      </c>
+      <c r="J1481">
+        <v>57726</v>
+      </c>
+      <c r="K1481">
+        <v>1</v>
+      </c>
+      <c r="AB1481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1482">
+        <v>11914</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1482">
+        <v>7201</v>
+      </c>
+      <c r="D1482">
+        <v>70103</v>
+      </c>
+      <c r="E1482">
+        <v>6</v>
+      </c>
+      <c r="F1482">
+        <v>18</v>
+      </c>
+      <c r="G1482" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1482" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1482">
+        <v>71</v>
+      </c>
+      <c r="J1482">
+        <v>57733</v>
+      </c>
+      <c r="K1482">
+        <v>1</v>
+      </c>
+      <c r="O1482">
+        <v>21</v>
+      </c>
+      <c r="AB1482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1483">
+        <v>11915</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C1483">
+        <v>7103</v>
+      </c>
+      <c r="D1483">
+        <v>70403</v>
+      </c>
+      <c r="E1483">
+        <v>7</v>
+      </c>
+      <c r="F1483">
+        <v>19</v>
+      </c>
+      <c r="G1483" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1483" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1483">
+        <v>71</v>
+      </c>
+      <c r="J1483">
+        <v>57742</v>
+      </c>
+      <c r="K1483">
+        <v>6</v>
+      </c>
+      <c r="V1483">
+        <v>92</v>
+      </c>
+      <c r="AB1483">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1484">
+        <v>11918</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C1484">
+        <v>7103</v>
+      </c>
+      <c r="D1484">
+        <v>70403</v>
+      </c>
+      <c r="E1484">
+        <v>7</v>
+      </c>
+      <c r="F1484">
+        <v>22</v>
+      </c>
+      <c r="G1484" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1484" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1484">
+        <v>71</v>
+      </c>
+      <c r="J1484">
+        <v>57756</v>
+      </c>
+      <c r="K1484">
+        <v>3</v>
+      </c>
+      <c r="N1484">
+        <v>11</v>
+      </c>
+      <c r="AB1484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1485">
+        <v>11919</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1485">
+        <v>7203</v>
+      </c>
+      <c r="D1485">
+        <v>70403</v>
+      </c>
+      <c r="E1485">
+        <v>7</v>
+      </c>
+      <c r="F1485">
+        <v>23</v>
+      </c>
+      <c r="G1485" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1485" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1485">
+        <v>71</v>
+      </c>
+      <c r="J1485">
+        <v>57759</v>
+      </c>
+      <c r="K1485">
+        <v>3</v>
+      </c>
+      <c r="Q1485" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB1485">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1486">
+        <v>11920</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C1486">
+        <v>7203</v>
+      </c>
+      <c r="D1486">
+        <v>70403</v>
+      </c>
+      <c r="E1486">
+        <v>7</v>
+      </c>
+      <c r="F1486">
+        <v>24</v>
+      </c>
+      <c r="G1486" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1486" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1486">
+        <v>71</v>
+      </c>
+      <c r="J1486">
+        <v>57762</v>
+      </c>
+      <c r="K1486">
+        <v>2</v>
+      </c>
+      <c r="O1486">
+        <v>21</v>
+      </c>
+      <c r="AB1486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1487">
+        <v>11921</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C1487">
+        <v>7103</v>
+      </c>
+      <c r="D1487">
+        <v>70403</v>
+      </c>
+      <c r="E1487">
+        <v>7</v>
+      </c>
+      <c r="F1487">
+        <v>25</v>
+      </c>
+      <c r="G1487" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1487" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1487">
+        <v>71</v>
+      </c>
+      <c r="J1487">
+        <v>57766</v>
+      </c>
+      <c r="K1487">
+        <v>1</v>
+      </c>
+      <c r="O1487">
+        <v>21</v>
+      </c>
+      <c r="AB1487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1488">
+        <v>11922</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C1488">
+        <v>7203</v>
+      </c>
+      <c r="D1488">
+        <v>70403</v>
+      </c>
+      <c r="E1488">
+        <v>7</v>
+      </c>
+      <c r="F1488">
+        <v>26</v>
+      </c>
+      <c r="G1488" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1488" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1488">
+        <v>71</v>
+      </c>
+      <c r="J1488">
+        <v>57772</v>
+      </c>
+      <c r="K1488">
+        <v>2</v>
+      </c>
+      <c r="AB1488">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1489">
+        <v>11934</v>
+      </c>
+      <c r="B1489" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C1489">
+        <v>3624</v>
+      </c>
+      <c r="D1489">
+        <v>30608</v>
+      </c>
+      <c r="E1489">
+        <v>14</v>
+      </c>
+      <c r="F1489">
+        <v>60</v>
+      </c>
+      <c r="G1489" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1489" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1489">
+        <v>94</v>
+      </c>
+      <c r="J1489">
+        <v>57832</v>
+      </c>
+      <c r="K1489">
+        <v>1</v>
+      </c>
+      <c r="U1489">
+        <v>82</v>
+      </c>
+      <c r="AB1489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1490">
+        <v>11971</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1490">
+        <v>4207</v>
+      </c>
+      <c r="D1490">
+        <v>40806</v>
+      </c>
+      <c r="E1490">
+        <v>14</v>
+      </c>
+      <c r="F1490">
+        <v>4</v>
+      </c>
+      <c r="G1490" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1490" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1490">
+        <v>53</v>
+      </c>
+      <c r="J1490">
+        <v>58031</v>
+      </c>
+      <c r="K1490">
+        <v>1</v>
+      </c>
+      <c r="AB1490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1491">
+        <v>11971</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1491">
+        <v>4207</v>
+      </c>
+      <c r="D1491">
+        <v>40806</v>
+      </c>
+      <c r="E1491">
+        <v>14</v>
+      </c>
+      <c r="F1491">
+        <v>4</v>
+      </c>
+      <c r="G1491" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1491" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1491">
+        <v>53</v>
+      </c>
+      <c r="J1491">
+        <v>58034</v>
+      </c>
+      <c r="K1491">
+        <v>4</v>
+      </c>
+      <c r="AB1491">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1492">
+        <v>11971</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1492">
+        <v>4207</v>
+      </c>
+      <c r="D1492">
+        <v>40806</v>
+      </c>
+      <c r="E1492">
+        <v>14</v>
+      </c>
+      <c r="F1492">
+        <v>4</v>
+      </c>
+      <c r="G1492" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1492" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1492">
+        <v>53</v>
+      </c>
+      <c r="J1492">
+        <v>58036</v>
+      </c>
+      <c r="K1492">
+        <v>6</v>
+      </c>
+      <c r="AB1492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1493">
+        <v>11975</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C1493">
+        <v>3620</v>
+      </c>
+      <c r="E1493">
+        <v>0</v>
+      </c>
+      <c r="F1493">
+        <v>65</v>
+      </c>
+      <c r="G1493" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1493" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1493">
+        <v>91</v>
+      </c>
+      <c r="J1493">
+        <v>58050</v>
+      </c>
+      <c r="K1493">
+        <v>1</v>
+      </c>
+      <c r="AA1493" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1494">
+        <v>11999</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C1494">
+        <v>1202</v>
+      </c>
+      <c r="D1494">
+        <v>10304</v>
+      </c>
+      <c r="E1494">
+        <v>4</v>
+      </c>
+      <c r="F1494">
+        <v>32</v>
+      </c>
+      <c r="G1494" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1494" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1494">
+        <v>14</v>
+      </c>
+      <c r="J1494">
+        <v>58175</v>
+      </c>
+      <c r="K1494">
+        <v>4</v>
+      </c>
+      <c r="N1494" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1494">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1495">
+        <v>12007</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C1495">
+        <v>1102</v>
+      </c>
+      <c r="D1495">
+        <v>10304</v>
+      </c>
+      <c r="E1495">
+        <v>4</v>
+      </c>
+      <c r="F1495">
+        <v>40</v>
+      </c>
+      <c r="G1495" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1495" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1495">
+        <v>14</v>
+      </c>
+      <c r="J1495">
+        <v>58211</v>
+      </c>
+      <c r="K1495">
+        <v>4</v>
+      </c>
+      <c r="AB1495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1496">
+        <v>12009</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C1496">
+        <v>1102</v>
+      </c>
+      <c r="D1496">
+        <v>10304</v>
+      </c>
+      <c r="E1496">
+        <v>4</v>
+      </c>
+      <c r="F1496">
+        <v>42</v>
+      </c>
+      <c r="G1496" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1496" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1496">
+        <v>14</v>
+      </c>
+      <c r="J1496">
+        <v>58216</v>
+      </c>
+      <c r="K1496">
+        <v>1</v>
+      </c>
+      <c r="O1496">
+        <v>23</v>
+      </c>
+      <c r="AB1496">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1497">
+        <v>12010</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C1497">
+        <v>1202</v>
+      </c>
+      <c r="D1497">
+        <v>10304</v>
+      </c>
+      <c r="E1497">
+        <v>4</v>
+      </c>
+      <c r="F1497">
+        <v>43</v>
+      </c>
+      <c r="G1497" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1497" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1497">
+        <v>14</v>
+      </c>
+      <c r="J1497">
+        <v>58225</v>
+      </c>
+      <c r="K1497">
+        <v>5</v>
+      </c>
+      <c r="O1497">
+        <v>23</v>
+      </c>
+      <c r="AB1497">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1498">
+        <v>12011</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C1498">
+        <v>1202</v>
+      </c>
+      <c r="D1498">
+        <v>10304</v>
+      </c>
+      <c r="E1498">
+        <v>4</v>
+      </c>
+      <c r="F1498">
+        <v>44</v>
+      </c>
+      <c r="G1498" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1498" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1498">
+        <v>14</v>
+      </c>
+      <c r="J1498">
+        <v>58228</v>
+      </c>
+      <c r="K1498">
+        <v>1</v>
+      </c>
+      <c r="Y1498">
+        <v>122</v>
+      </c>
+      <c r="AB1498">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataset/Part 6_3_3_ Acute Illness health seeking and expenditure tracking.xlsx
+++ b/dataset/Part 6_3_3_ Acute Illness health seeking and expenditure tracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-28-today (1)\2025-11-28-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09842D9B-E1B0-49B4-A0F1-D2B0F0147165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B166C2AC-211E-4511-8435-697213692D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4993" uniqueCount="1378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5523" uniqueCount="1547">
   <si>
     <t>ID</t>
   </si>
@@ -4166,6 +4166,516 @@
   </si>
   <si>
     <t>dce67f7d-3192-4b46-9822-85562317158a</t>
+  </si>
+  <si>
+    <t>ff4b95a4-5501-4bd0-9d94-dfde1adeb233</t>
+  </si>
+  <si>
+    <t>2f313907-b970-4302-906d-e55acdeb1b9b</t>
+  </si>
+  <si>
+    <t>cd9f57e6-8645-4007-862f-1107814dd344</t>
+  </si>
+  <si>
+    <t>ce45d277-4564-40dc-944d-c2365aee90c2</t>
+  </si>
+  <si>
+    <t>8e2b68af-32ab-45d1-9417-6f54f8de771f</t>
+  </si>
+  <si>
+    <t>3dbc972a-99c9-47b3-bd0e-dcc4eb1d98ef</t>
+  </si>
+  <si>
+    <t>982fbdad-9578-41b2-bd21-2269df0744dd</t>
+  </si>
+  <si>
+    <t>ddf440c9-a454-4da3-8b80-10edc09a0ae7</t>
+  </si>
+  <si>
+    <t>df49a0f5-ceeb-45c0-af49-d2b4e043f52f</t>
+  </si>
+  <si>
+    <t>0cac8da4-689a-46b9-ac7e-16f567b1d63b</t>
+  </si>
+  <si>
+    <t>2a1bf168-f018-4912-9114-a12548214735</t>
+  </si>
+  <si>
+    <t>833c93bc-b74a-4d26-b6b1-a8c8bd6612e9</t>
+  </si>
+  <si>
+    <t>eca4090c-34c0-463c-827d-ae9217063785</t>
+  </si>
+  <si>
+    <t>448bb129-b2df-48cd-843d-0905320a243f</t>
+  </si>
+  <si>
+    <t>ed15a6ff-1d35-4c76-b89f-16fd8d016d3b</t>
+  </si>
+  <si>
+    <t>13ddeab8-3e74-44d3-b157-efaf35e7fe19</t>
+  </si>
+  <si>
+    <t>COUGH SYRUP</t>
+  </si>
+  <si>
+    <t>ddeb9c91-6fe2-43ea-872e-6f9c6371ece5</t>
+  </si>
+  <si>
+    <t>c9d9cec9-7c83-4427-a8aa-e569d0704f8d</t>
+  </si>
+  <si>
+    <t>f211587b-8c71-4f1f-82cc-b8a2dbcff030</t>
+  </si>
+  <si>
+    <t>80b5c53f-aaa8-4515-bc1a-4dd079553729</t>
+  </si>
+  <si>
+    <t>HALF FREE AND HALF CASH</t>
+  </si>
+  <si>
+    <t>1130b451-8e1e-4867-8ee0-fe179dec1cb7</t>
+  </si>
+  <si>
+    <t>SINEX 
+COUGH SYRUP 
+PARACETAMOL</t>
+  </si>
+  <si>
+    <t>d1adb6d7-afb9-4101-a9ff-89879660738e</t>
+  </si>
+  <si>
+    <t>NIKO 
+ANTIBIOTICS</t>
+  </si>
+  <si>
+    <t>1dd015c9-3f73-41b1-9c4c-4088f52d5412</t>
+  </si>
+  <si>
+    <t>AAUSADI UPACHAR NAGAREKO</t>
+  </si>
+  <si>
+    <t>4bb8535a-197d-4fae-8eb3-f32af614ef24</t>
+  </si>
+  <si>
+    <t>b3dbcd54-cf0e-4f20-815e-90c583ed3fbb</t>
+  </si>
+  <si>
+    <t>776535bf-dfbb-4400-ab86-c8797dfa945d</t>
+  </si>
+  <si>
+    <t>105fb314-cb6e-4a9e-a5d0-3031ee5151f6</t>
+  </si>
+  <si>
+    <t>574a2e61-a016-4ab0-9aa8-6bda970e0446</t>
+  </si>
+  <si>
+    <t>38dc9f98-00b8-41e1-a18b-f7ab094f592d</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>745c865a-41af-4e66-9690-c814678f82f2</t>
+  </si>
+  <si>
+    <t>36e03b5f-5959-4600-8e4e-26cef3c19c58</t>
+  </si>
+  <si>
+    <t>bba20690-da24-45a1-ac67-8ecb6ea8b183</t>
+  </si>
+  <si>
+    <t>47b49e8e-fd38-497e-8388-c5d53913848d</t>
+  </si>
+  <si>
+    <t>355a6681-32bb-4323-92b2-a302b4a681ce</t>
+  </si>
+  <si>
+    <t>44201d39-eef6-4920-b762-87c9e4bed2ea</t>
+  </si>
+  <si>
+    <t>cc272699-afb2-4e9f-81fe-0bfebb85a40d</t>
+  </si>
+  <si>
+    <t>AAUSADI NAI NAKHAYEKO</t>
+  </si>
+  <si>
+    <t>46312954-42c9-44eb-a0ee-f0ba9f412962</t>
+  </si>
+  <si>
+    <t>c0cff2d4-fcbc-477c-8c77-41aecd6d10c3</t>
+  </si>
+  <si>
+    <t>141, SUPREME,</t>
+  </si>
+  <si>
+    <t>e2b5c099-853f-4431-8011-afa20120861b</t>
+  </si>
+  <si>
+    <t>c2d301a1-3cae-446e-850c-8670132903d4</t>
+  </si>
+  <si>
+    <t>7c85594c-3e29-4b0e-a8a6-d728ef8cc69d</t>
+  </si>
+  <si>
+    <t>f5107678-9828-4886-a0ac-d3a70ea121c5</t>
+  </si>
+  <si>
+    <t>92ba3436-47eb-42a3-a30d-71c2c5983de2</t>
+  </si>
+  <si>
+    <t>9f78db29-ec22-47a0-b085-1bfe8c65b713</t>
+  </si>
+  <si>
+    <t>DOXYCOCLINE100MG,CEFIXINE, ROFAST</t>
+  </si>
+  <si>
+    <t>321a448a-86b8-4fd0-81e8-dfc0df7eea1e</t>
+  </si>
+  <si>
+    <t>624e4e87-65d5-43bc-b23c-44e67a4785d4</t>
+  </si>
+  <si>
+    <t>f0759853-976a-47cd-8260-b4afd510bf86</t>
+  </si>
+  <si>
+    <t>22bf0e9e-668e-471c-a7de-784519c5c114</t>
+  </si>
+  <si>
+    <t>21, 23, 22</t>
+  </si>
+  <si>
+    <t>8963dc25-c206-454c-8cb3-ea1df9505483</t>
+  </si>
+  <si>
+    <t>d8c5d888-20ec-4401-9a95-7ff561e3ca80</t>
+  </si>
+  <si>
+    <t>590b52f9-3e49-4063-af69-538fbfb04b03</t>
+  </si>
+  <si>
+    <t>BETADIN,GAUGE</t>
+  </si>
+  <si>
+    <t>18b9b143-27b3-4693-b95e-13ad67784360</t>
+  </si>
+  <si>
+    <t>NIKO</t>
+  </si>
+  <si>
+    <t>cc9c7d3f-a1ee-4df7-b34c-2f44903a357c</t>
+  </si>
+  <si>
+    <t>c6d62aef-f642-4301-a974-39f85075ad46</t>
+  </si>
+  <si>
+    <t>THORAI AAFNO KHALTIKO</t>
+  </si>
+  <si>
+    <t>307c1971-d156-461b-a0f0-95d249c8a05d</t>
+  </si>
+  <si>
+    <t>123, 122, 121</t>
+  </si>
+  <si>
+    <t>39341d30-6cfc-4d95-bca3-083164937422</t>
+  </si>
+  <si>
+    <t>84332e61-d4fe-479d-85ef-7dda91a300bd</t>
+  </si>
+  <si>
+    <t>ad330f68-3f37-4ee8-832b-81e2217af763</t>
+  </si>
+  <si>
+    <t>79571e9b-72c6-4f74-9e80-48a4ac3bc46d</t>
+  </si>
+  <si>
+    <t>ee3e5104-7baf-43f5-8274-21529870089b</t>
+  </si>
+  <si>
+    <t>1776bc30-86df-47ab-b615-f640b65e4a0b</t>
+  </si>
+  <si>
+    <t>3eb5203d-c0d1-48a8-b341-b4c201cbe611</t>
+  </si>
+  <si>
+    <t>526786fb-f603-43f7-bd2a-b3854f4d5520</t>
+  </si>
+  <si>
+    <t>e165e728-1f5f-4da5-8693-5a73ff63e7b5</t>
+  </si>
+  <si>
+    <t>ed4232df-6ea9-41b1-a4c9-92ce5a1fb72e</t>
+  </si>
+  <si>
+    <t>23, 21, 22</t>
+  </si>
+  <si>
+    <t>4e38e751-154c-4c2d-8eb9-3995dd4293ae</t>
+  </si>
+  <si>
+    <t>a8720150-68f0-4583-9b09-7d54dc0854e8</t>
+  </si>
+  <si>
+    <t>35ff98dc-5f4f-4007-b81b-d9da0ec8a72c</t>
+  </si>
+  <si>
+    <t>d42af399-7fc4-4fdc-bd64-f106be358d85</t>
+  </si>
+  <si>
+    <t>75754554-12fd-4b1d-856c-1535f0e2713e</t>
+  </si>
+  <si>
+    <t>c24f18fa-eb4b-414d-b2d6-92eed9e74994</t>
+  </si>
+  <si>
+    <t>MEDROL</t>
+  </si>
+  <si>
+    <t>e474cec5-c58a-4212-86ab-b31848fa19a5</t>
+  </si>
+  <si>
+    <t>b9e4f725-a180-4151-9ad6-a9829de993d6</t>
+  </si>
+  <si>
+    <t>KUNAI TREATMENT NA GAREKO</t>
+  </si>
+  <si>
+    <t>c5847474-047f-4dea-ae01-e5c09585c32f</t>
+  </si>
+  <si>
+    <t>43, 41</t>
+  </si>
+  <si>
+    <t>2c650208-9d25-426b-8314-247f5de04079</t>
+  </si>
+  <si>
+    <t>4a855b2e-5ae7-4f17-bcdb-bb7857723e0e</t>
+  </si>
+  <si>
+    <t>bed65f5f-81a6-4212-98be-5892549acf8d</t>
+  </si>
+  <si>
+    <t>NO CHECK</t>
+  </si>
+  <si>
+    <t>20b56f21-0e9c-45d9-939b-1021e9b3f25d</t>
+  </si>
+  <si>
+    <t>f930a696-e29d-4245-b718-519571fbe6ce</t>
+  </si>
+  <si>
+    <t>2a844aeb-4585-4e4d-b317-1294ddfe704c</t>
+  </si>
+  <si>
+    <t>e3620181-c6c4-4c72-a7d5-e28f3abf75d1</t>
+  </si>
+  <si>
+    <t>817ee771-1952-427c-9c43-22025d0253b4</t>
+  </si>
+  <si>
+    <t>6b77a5be-4ad6-48b6-b587-4c08349993f9</t>
+  </si>
+  <si>
+    <t>83, 81</t>
+  </si>
+  <si>
+    <t>b87cf70d-16b3-4122-8f7b-cfaff6d28db7</t>
+  </si>
+  <si>
+    <t>ddcd897b-829e-4a6b-a243-d2003a880fb4</t>
+  </si>
+  <si>
+    <t>694952d4-9e2b-4b12-b95f-5c77bbcfe252</t>
+  </si>
+  <si>
+    <t>b513229e-32f5-4949-b79c-eb384d617bb6</t>
+  </si>
+  <si>
+    <t>305fcdef-ae4d-4691-8a22-12b448304cf3</t>
+  </si>
+  <si>
+    <t>7b892f6b-94a3-4f05-b3e0-aaea09e44bb3</t>
+  </si>
+  <si>
+    <t>d04a265c-bf6b-40ae-b94f-e8fa0deb8b45</t>
+  </si>
+  <si>
+    <t>c22c75a9-e062-4681-b9ae-d095c5baddeb</t>
+  </si>
+  <si>
+    <t>4d688ebc-eafb-4e87-baf5-b10ef86d6cc0</t>
+  </si>
+  <si>
+    <t>60eff54a-1c25-4c6f-bc13-73c97cea30ba</t>
+  </si>
+  <si>
+    <t>7203e045-085b-41a9-9d44-63b26a486ec4</t>
+  </si>
+  <si>
+    <t>cf72101d-d4ba-482a-b682-72c144f4c6a0</t>
+  </si>
+  <si>
+    <t>KATAI NAGAYEKO</t>
+  </si>
+  <si>
+    <t>a441b901-2b55-4ce1-86ba-8384ae9dc940</t>
+  </si>
+  <si>
+    <t>1aa7172b-7b76-459b-be70-a24e40be0202</t>
+  </si>
+  <si>
+    <t>123, 122</t>
+  </si>
+  <si>
+    <t>98e9c195-5f1b-4ff2-89be-d210cfbf04e4</t>
+  </si>
+  <si>
+    <t>10fb58ef-6769-42c6-bdf3-9be1963f6b8e</t>
+  </si>
+  <si>
+    <t>23, 21</t>
+  </si>
+  <si>
+    <t>819e5e5e-b253-4bcc-938d-50e0a2af5483</t>
+  </si>
+  <si>
+    <t>NIKO MEDICINE DENU BHAYO</t>
+  </si>
+  <si>
+    <t>a5ffc94b-3549-4b83-9ff2-05ced84c5384</t>
+  </si>
+  <si>
+    <t>9f5a8308-3465-4cf7-baf6-af1cd3ec044e</t>
+  </si>
+  <si>
+    <t>9ac3e5e1-062d-4ca3-b3f5-bd0143b43705</t>
+  </si>
+  <si>
+    <t>22eaceea-9ed9-4b66-be93-d9f817766b88</t>
+  </si>
+  <si>
+    <t>b21e9c03-e14c-41bf-a8a1-27f7f734f14a</t>
+  </si>
+  <si>
+    <t>788902c1-be46-4fe1-b59e-a34f45da76d3</t>
+  </si>
+  <si>
+    <t>93ea0966-651d-440a-a667-ba50b0f23c70</t>
+  </si>
+  <si>
+    <t>80dca606-7895-4491-ac76-2c6d98f9f54f</t>
+  </si>
+  <si>
+    <t>123, 121, 122</t>
+  </si>
+  <si>
+    <t>b173dc52-74e0-4471-b0ce-2d89747f7d4c</t>
+  </si>
+  <si>
+    <t>KUNAI MEDICINE NA KHAKO KATI NA GAYEKO</t>
+  </si>
+  <si>
+    <t>42d3c76e-729a-4c29-85ae-c28639fed3e0</t>
+  </si>
+  <si>
+    <t>1,96</t>
+  </si>
+  <si>
+    <t>SSF LE BILL KO RAKAM NATIRDIYEKO</t>
+  </si>
+  <si>
+    <t>f7b8f0a4-f52a-400e-b24c-9acb81da8d46</t>
+  </si>
+  <si>
+    <t>fafceded-58b4-4656-a50f-84dba133028c</t>
+  </si>
+  <si>
+    <t>f59235c7-6bb2-4dfe-aeaf-86ce0ed2307b</t>
+  </si>
+  <si>
+    <t>SSF CLAIM GAREKO TARA NAKUNAI JAAF AAUO NA PAISA</t>
+  </si>
+  <si>
+    <t>3309a1fc-22df-44be-a476-073010550821</t>
+  </si>
+  <si>
+    <t>8673ab55-74ba-438e-a41c-0855a7c761e4</t>
+  </si>
+  <si>
+    <t>8d430a28-3d1b-480c-872c-58bcc2a3700e</t>
+  </si>
+  <si>
+    <t>43, 42</t>
+  </si>
+  <si>
+    <t>22936b6a-3882-4c1d-8650-6453fd21fc1b</t>
+  </si>
+  <si>
+    <t>f34dfa64-d92e-4767-80f0-1c79c17b79d1</t>
+  </si>
+  <si>
+    <t>781ca324-c0b3-41a2-98e4-58fe5268cb6d</t>
+  </si>
+  <si>
+    <t>57c5e6e9-cecf-453b-8021-024c659f7b31</t>
+  </si>
+  <si>
+    <t>a45d8643-b581-48f8-a5e9-415801a3221f</t>
+  </si>
+  <si>
+    <t>94381e73-c738-487b-8371-1532ebad1e2b</t>
+  </si>
+  <si>
+    <t>855c0c6f-7f32-450e-8b97-8c33bcd8e066</t>
+  </si>
+  <si>
+    <t>c04004cb-f10e-4038-808a-ccd0f66de452</t>
+  </si>
+  <si>
+    <t>23, 22</t>
+  </si>
+  <si>
+    <t>28f838dd-719f-49e4-8f03-8ae376b29988</t>
+  </si>
+  <si>
+    <t>814cfd62-d563-47ac-8ea5-f947a3d37df3</t>
+  </si>
+  <si>
+    <t>e128c5fa-1e3f-4c0d-8b04-f85a86c549cc</t>
+  </si>
+  <si>
+    <t>MEDICINE KO NAM YAAD NABHAKO</t>
+  </si>
+  <si>
+    <t>4d2b1715-bc94-4d91-8e5e-b3e0ebe12de7</t>
+  </si>
+  <si>
+    <t>NO TREATMENT HOMEMADE REMEDY HARU KHUWAUNU HUDAI</t>
+  </si>
+  <si>
+    <t>6ce7164e-1c9e-4b3f-9c04-33452685484a</t>
+  </si>
+  <si>
+    <t>3b78426c-851a-4166-aa92-70dac28fcafa</t>
+  </si>
+  <si>
+    <t>5d49d88f-8556-4fcb-a923-5745c69e93c6</t>
+  </si>
+  <si>
+    <t>6a68dd1c-6779-4ea1-bee6-406b96bba539</t>
+  </si>
+  <si>
+    <t>39ff06cc-2874-4abc-a477-28a70d833e5f</t>
+  </si>
+  <si>
+    <t>046ccbe8-60c5-4c3e-9043-89f1c42e1c35</t>
+  </si>
+  <si>
+    <t>KEHI NAGAREKO</t>
+  </si>
+  <si>
+    <t>d74e8aab-bdaa-48f8-b526-f319c99b6815</t>
   </si>
 </sst>
 </file>
@@ -4211,10 +4721,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4519,7 +5032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1498"/>
+  <dimension ref="A1:AC1651"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -63685,6 +64198,6102 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1499" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1499">
+        <v>12047</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C1499">
+        <v>3359</v>
+      </c>
+      <c r="D1499">
+        <v>30802</v>
+      </c>
+      <c r="E1499">
+        <v>13</v>
+      </c>
+      <c r="F1499">
+        <v>12</v>
+      </c>
+      <c r="G1499" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1499" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1499">
+        <v>57</v>
+      </c>
+      <c r="J1499">
+        <v>58440</v>
+      </c>
+      <c r="K1499">
+        <v>3</v>
+      </c>
+      <c r="AB1499">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1500">
+        <v>12049</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C1500">
+        <v>3382</v>
+      </c>
+      <c r="D1500">
+        <v>30802</v>
+      </c>
+      <c r="E1500">
+        <v>3</v>
+      </c>
+      <c r="F1500">
+        <v>14</v>
+      </c>
+      <c r="G1500" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1500" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1500">
+        <v>57</v>
+      </c>
+      <c r="J1500">
+        <v>58444</v>
+      </c>
+      <c r="K1500">
+        <v>1</v>
+      </c>
+      <c r="AB1500">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1501">
+        <v>12051</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C1501">
+        <v>3628</v>
+      </c>
+      <c r="D1501">
+        <v>30802</v>
+      </c>
+      <c r="E1501">
+        <v>2</v>
+      </c>
+      <c r="F1501">
+        <v>16</v>
+      </c>
+      <c r="G1501" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1501" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1501">
+        <v>57</v>
+      </c>
+      <c r="J1501">
+        <v>58453</v>
+      </c>
+      <c r="K1501">
+        <v>5</v>
+      </c>
+      <c r="X1501">
+        <v>112</v>
+      </c>
+      <c r="AB1501">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1502">
+        <v>12053</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C1502">
+        <v>3628</v>
+      </c>
+      <c r="D1502">
+        <v>30802</v>
+      </c>
+      <c r="E1502">
+        <v>0</v>
+      </c>
+      <c r="F1502">
+        <v>18</v>
+      </c>
+      <c r="G1502" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1502" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1502">
+        <v>57</v>
+      </c>
+      <c r="J1502">
+        <v>58461</v>
+      </c>
+      <c r="K1502">
+        <v>3</v>
+      </c>
+      <c r="AB1502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1503">
+        <v>12074</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C1503">
+        <v>3522</v>
+      </c>
+      <c r="E1503">
+        <v>0</v>
+      </c>
+      <c r="F1503">
+        <v>36</v>
+      </c>
+      <c r="G1503" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1503" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1503">
+        <v>92</v>
+      </c>
+      <c r="J1503">
+        <v>58577</v>
+      </c>
+      <c r="K1503">
+        <v>2</v>
+      </c>
+      <c r="AA1503">
+        <v>141</v>
+      </c>
+      <c r="AB1503">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1504">
+        <v>12077</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C1504">
+        <v>3677</v>
+      </c>
+      <c r="D1504">
+        <v>30608</v>
+      </c>
+      <c r="E1504">
+        <v>28</v>
+      </c>
+      <c r="F1504">
+        <v>70</v>
+      </c>
+      <c r="G1504" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1504" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1504">
+        <v>93</v>
+      </c>
+      <c r="J1504">
+        <v>58590</v>
+      </c>
+      <c r="K1504">
+        <v>2</v>
+      </c>
+      <c r="AA1504">
+        <v>141</v>
+      </c>
+      <c r="AB1504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1505">
+        <v>12081</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C1505">
+        <v>2106</v>
+      </c>
+      <c r="D1505">
+        <v>20514</v>
+      </c>
+      <c r="E1505">
+        <v>6</v>
+      </c>
+      <c r="F1505">
+        <v>48</v>
+      </c>
+      <c r="G1505" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1505" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1505">
+        <v>23</v>
+      </c>
+      <c r="J1505">
+        <v>58616</v>
+      </c>
+      <c r="K1505">
+        <v>8</v>
+      </c>
+      <c r="O1505" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1506">
+        <v>12082</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C1506">
+        <v>2106</v>
+      </c>
+      <c r="D1506">
+        <v>20514</v>
+      </c>
+      <c r="E1506">
+        <v>6</v>
+      </c>
+      <c r="F1506">
+        <v>49</v>
+      </c>
+      <c r="G1506" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1506" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1506">
+        <v>23</v>
+      </c>
+      <c r="J1506">
+        <v>58618</v>
+      </c>
+      <c r="K1506">
+        <v>2</v>
+      </c>
+      <c r="O1506">
+        <v>21</v>
+      </c>
+      <c r="AB1506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1507">
+        <v>12083</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1507">
+        <v>2106</v>
+      </c>
+      <c r="D1507">
+        <v>20514</v>
+      </c>
+      <c r="E1507">
+        <v>6</v>
+      </c>
+      <c r="F1507">
+        <v>50</v>
+      </c>
+      <c r="G1507" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1507" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1507">
+        <v>23</v>
+      </c>
+      <c r="J1507">
+        <v>58627</v>
+      </c>
+      <c r="K1507">
+        <v>1</v>
+      </c>
+      <c r="Y1507" t="s">
+        <v>194</v>
+      </c>
+      <c r="AB1507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1508">
+        <v>12084</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C1508">
+        <v>2206</v>
+      </c>
+      <c r="D1508">
+        <v>20514</v>
+      </c>
+      <c r="E1508">
+        <v>2</v>
+      </c>
+      <c r="F1508">
+        <v>51</v>
+      </c>
+      <c r="G1508" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1508" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1508">
+        <v>23</v>
+      </c>
+      <c r="J1508">
+        <v>58636</v>
+      </c>
+      <c r="K1508">
+        <v>2</v>
+      </c>
+      <c r="AB1508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1509">
+        <v>12085</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C1509">
+        <v>2206</v>
+      </c>
+      <c r="D1509">
+        <v>20514</v>
+      </c>
+      <c r="E1509">
+        <v>2</v>
+      </c>
+      <c r="F1509">
+        <v>52</v>
+      </c>
+      <c r="G1509" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1509" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1509">
+        <v>23</v>
+      </c>
+      <c r="J1509">
+        <v>58641</v>
+      </c>
+      <c r="K1509">
+        <v>1</v>
+      </c>
+      <c r="O1509" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1510">
+        <v>12085</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C1510">
+        <v>2206</v>
+      </c>
+      <c r="D1510">
+        <v>20514</v>
+      </c>
+      <c r="E1510">
+        <v>2</v>
+      </c>
+      <c r="F1510">
+        <v>52</v>
+      </c>
+      <c r="G1510" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1510" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1510">
+        <v>23</v>
+      </c>
+      <c r="J1510">
+        <v>58644</v>
+      </c>
+      <c r="K1510">
+        <v>4</v>
+      </c>
+      <c r="O1510" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1511">
+        <v>12087</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C1511">
+        <v>2616</v>
+      </c>
+      <c r="E1511">
+        <v>0</v>
+      </c>
+      <c r="F1511">
+        <v>54</v>
+      </c>
+      <c r="G1511" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1511" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1511">
+        <v>23</v>
+      </c>
+      <c r="J1511">
+        <v>58653</v>
+      </c>
+      <c r="K1511">
+        <v>1</v>
+      </c>
+      <c r="O1511" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1512">
+        <v>12091</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C1512">
+        <v>3504</v>
+      </c>
+      <c r="E1512">
+        <v>0</v>
+      </c>
+      <c r="F1512">
+        <v>72</v>
+      </c>
+      <c r="G1512" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1512" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1512">
+        <v>91</v>
+      </c>
+      <c r="J1512">
+        <v>58670</v>
+      </c>
+      <c r="K1512">
+        <v>1</v>
+      </c>
+      <c r="O1512" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1512">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1513">
+        <v>12092</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C1513">
+        <v>2516</v>
+      </c>
+      <c r="D1513">
+        <v>20502</v>
+      </c>
+      <c r="E1513">
+        <v>11</v>
+      </c>
+      <c r="F1513">
+        <v>55</v>
+      </c>
+      <c r="G1513" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1513" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1513">
+        <v>23</v>
+      </c>
+      <c r="J1513">
+        <v>58675</v>
+      </c>
+      <c r="K1513">
+        <v>2</v>
+      </c>
+      <c r="AA1513" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1513">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1514">
+        <v>12093</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C1514">
+        <v>1107</v>
+      </c>
+      <c r="D1514">
+        <v>11102</v>
+      </c>
+      <c r="E1514">
+        <v>3</v>
+      </c>
+      <c r="F1514">
+        <v>46</v>
+      </c>
+      <c r="G1514" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1514" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1514">
+        <v>14</v>
+      </c>
+      <c r="J1514">
+        <v>58682</v>
+      </c>
+      <c r="K1514">
+        <v>4</v>
+      </c>
+      <c r="AB1514">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1515">
+        <v>12094</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C1515">
+        <v>1207</v>
+      </c>
+      <c r="D1515">
+        <v>11102</v>
+      </c>
+      <c r="E1515">
+        <v>3</v>
+      </c>
+      <c r="F1515">
+        <v>48</v>
+      </c>
+      <c r="G1515" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1515" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1515">
+        <v>14</v>
+      </c>
+      <c r="J1515">
+        <v>58686</v>
+      </c>
+      <c r="K1515">
+        <v>4</v>
+      </c>
+      <c r="O1515">
+        <v>21</v>
+      </c>
+      <c r="AB1515">
+        <v>1</v>
+      </c>
+      <c r="AC1515" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1516">
+        <v>12102</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C1516">
+        <v>1107</v>
+      </c>
+      <c r="D1516">
+        <v>11102</v>
+      </c>
+      <c r="E1516">
+        <v>3</v>
+      </c>
+      <c r="F1516">
+        <v>51</v>
+      </c>
+      <c r="G1516" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1516" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1516">
+        <v>14</v>
+      </c>
+      <c r="J1516">
+        <v>58721</v>
+      </c>
+      <c r="K1516">
+        <v>6</v>
+      </c>
+      <c r="O1516">
+        <v>21</v>
+      </c>
+      <c r="AB1516">
+        <v>1</v>
+      </c>
+      <c r="AC1516" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1517">
+        <v>12103</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C1517">
+        <v>1207</v>
+      </c>
+      <c r="D1517">
+        <v>11102</v>
+      </c>
+      <c r="E1517">
+        <v>3</v>
+      </c>
+      <c r="F1517">
+        <v>52</v>
+      </c>
+      <c r="G1517" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1517" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1517">
+        <v>14</v>
+      </c>
+      <c r="J1517">
+        <v>58722</v>
+      </c>
+      <c r="K1517">
+        <v>1</v>
+      </c>
+      <c r="AB1517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1518">
+        <v>12103</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C1518">
+        <v>1207</v>
+      </c>
+      <c r="D1518">
+        <v>11102</v>
+      </c>
+      <c r="E1518">
+        <v>3</v>
+      </c>
+      <c r="F1518">
+        <v>52</v>
+      </c>
+      <c r="G1518" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1518" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1518">
+        <v>14</v>
+      </c>
+      <c r="J1518">
+        <v>58724</v>
+      </c>
+      <c r="K1518">
+        <v>3</v>
+      </c>
+      <c r="Q1518">
+        <v>41</v>
+      </c>
+      <c r="AB1518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1519">
+        <v>12104</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C1519">
+        <v>1107</v>
+      </c>
+      <c r="D1519">
+        <v>11102</v>
+      </c>
+      <c r="E1519">
+        <v>3</v>
+      </c>
+      <c r="F1519">
+        <v>53</v>
+      </c>
+      <c r="G1519" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1519" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1519">
+        <v>14</v>
+      </c>
+      <c r="J1519">
+        <v>58727</v>
+      </c>
+      <c r="K1519">
+        <v>2</v>
+      </c>
+      <c r="O1519">
+        <v>21</v>
+      </c>
+      <c r="AB1519">
+        <v>1</v>
+      </c>
+      <c r="AC1519" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1520">
+        <v>12107</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1520">
+        <v>1207</v>
+      </c>
+      <c r="D1520">
+        <v>11102</v>
+      </c>
+      <c r="E1520">
+        <v>3</v>
+      </c>
+      <c r="F1520">
+        <v>58</v>
+      </c>
+      <c r="G1520" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1520" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1520">
+        <v>14</v>
+      </c>
+      <c r="J1520">
+        <v>58736</v>
+      </c>
+      <c r="K1520">
+        <v>1</v>
+      </c>
+      <c r="O1520" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1520">
+        <v>96</v>
+      </c>
+      <c r="AC1520" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1521">
+        <v>12108</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C1521">
+        <v>1207</v>
+      </c>
+      <c r="D1521">
+        <v>11102</v>
+      </c>
+      <c r="E1521">
+        <v>3</v>
+      </c>
+      <c r="F1521">
+        <v>57</v>
+      </c>
+      <c r="G1521" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1521" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1521">
+        <v>14</v>
+      </c>
+      <c r="J1521">
+        <v>58741</v>
+      </c>
+      <c r="K1521">
+        <v>3</v>
+      </c>
+      <c r="AB1521">
+        <v>1</v>
+      </c>
+      <c r="AC1521" s="3" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1522">
+        <v>12110</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C1522">
+        <v>1207</v>
+      </c>
+      <c r="D1522">
+        <v>11102</v>
+      </c>
+      <c r="E1522">
+        <v>3</v>
+      </c>
+      <c r="F1522">
+        <v>56</v>
+      </c>
+      <c r="G1522" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1522" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1522">
+        <v>14</v>
+      </c>
+      <c r="J1522">
+        <v>58750</v>
+      </c>
+      <c r="K1522">
+        <v>4</v>
+      </c>
+      <c r="AB1522">
+        <v>1</v>
+      </c>
+      <c r="AC1522" s="3" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1523">
+        <v>12112</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C1523">
+        <v>2618</v>
+      </c>
+      <c r="D1523">
+        <v>20501</v>
+      </c>
+      <c r="E1523">
+        <v>1</v>
+      </c>
+      <c r="F1523">
+        <v>57</v>
+      </c>
+      <c r="G1523" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1523" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1523">
+        <v>23</v>
+      </c>
+      <c r="J1523">
+        <v>58752</v>
+      </c>
+      <c r="K1523">
+        <v>1</v>
+      </c>
+      <c r="AB1523">
+        <v>96</v>
+      </c>
+      <c r="AC1523" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1524">
+        <v>12118</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C1524">
+        <v>2501</v>
+      </c>
+      <c r="E1524">
+        <v>0</v>
+      </c>
+      <c r="F1524">
+        <v>39</v>
+      </c>
+      <c r="G1524" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1524" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1524">
+        <v>21</v>
+      </c>
+      <c r="J1524">
+        <v>58784</v>
+      </c>
+      <c r="K1524">
+        <v>3</v>
+      </c>
+      <c r="O1524" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1525">
+        <v>12124</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1525">
+        <v>2106</v>
+      </c>
+      <c r="D1525">
+        <v>20514</v>
+      </c>
+      <c r="E1525">
+        <v>6</v>
+      </c>
+      <c r="F1525">
+        <v>44</v>
+      </c>
+      <c r="G1525" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1525" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1525">
+        <v>21</v>
+      </c>
+      <c r="J1525">
+        <v>58811</v>
+      </c>
+      <c r="K1525">
+        <v>5</v>
+      </c>
+      <c r="AB1525" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1526">
+        <v>12127</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C1526">
+        <v>2206</v>
+      </c>
+      <c r="D1526">
+        <v>20514</v>
+      </c>
+      <c r="E1526">
+        <v>2</v>
+      </c>
+      <c r="F1526">
+        <v>47</v>
+      </c>
+      <c r="G1526" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1526" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1526">
+        <v>21</v>
+      </c>
+      <c r="J1526">
+        <v>58821</v>
+      </c>
+      <c r="K1526">
+        <v>2</v>
+      </c>
+      <c r="O1526">
+        <v>21</v>
+      </c>
+      <c r="AB1526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1527">
+        <v>12127</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C1527">
+        <v>2206</v>
+      </c>
+      <c r="D1527">
+        <v>20514</v>
+      </c>
+      <c r="E1527">
+        <v>2</v>
+      </c>
+      <c r="F1527">
+        <v>47</v>
+      </c>
+      <c r="G1527" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1527" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1527">
+        <v>21</v>
+      </c>
+      <c r="J1527">
+        <v>58823</v>
+      </c>
+      <c r="K1527">
+        <v>4</v>
+      </c>
+      <c r="O1527" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1528">
+        <v>12127</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C1528">
+        <v>2206</v>
+      </c>
+      <c r="D1528">
+        <v>20514</v>
+      </c>
+      <c r="E1528">
+        <v>2</v>
+      </c>
+      <c r="F1528">
+        <v>47</v>
+      </c>
+      <c r="G1528" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1528" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1528">
+        <v>21</v>
+      </c>
+      <c r="J1528">
+        <v>58825</v>
+      </c>
+      <c r="K1528">
+        <v>6</v>
+      </c>
+      <c r="O1528">
+        <v>23</v>
+      </c>
+      <c r="AB1528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1529">
+        <v>12130</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1529">
+        <v>2206</v>
+      </c>
+      <c r="D1529">
+        <v>20514</v>
+      </c>
+      <c r="E1529">
+        <v>2</v>
+      </c>
+      <c r="F1529">
+        <v>50</v>
+      </c>
+      <c r="G1529" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1529" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1529">
+        <v>21</v>
+      </c>
+      <c r="J1529">
+        <v>58848</v>
+      </c>
+      <c r="K1529">
+        <v>6</v>
+      </c>
+      <c r="O1529">
+        <v>23</v>
+      </c>
+      <c r="AB1529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1530">
+        <v>12130</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1530">
+        <v>2206</v>
+      </c>
+      <c r="D1530">
+        <v>20514</v>
+      </c>
+      <c r="E1530">
+        <v>2</v>
+      </c>
+      <c r="F1530">
+        <v>50</v>
+      </c>
+      <c r="G1530" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1530" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1530">
+        <v>21</v>
+      </c>
+      <c r="J1530">
+        <v>58852</v>
+      </c>
+      <c r="K1530">
+        <v>10</v>
+      </c>
+      <c r="O1530">
+        <v>23</v>
+      </c>
+      <c r="AB1530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1531">
+        <v>12130</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1531">
+        <v>2206</v>
+      </c>
+      <c r="D1531">
+        <v>20514</v>
+      </c>
+      <c r="E1531">
+        <v>2</v>
+      </c>
+      <c r="F1531">
+        <v>50</v>
+      </c>
+      <c r="G1531" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1531" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1531">
+        <v>21</v>
+      </c>
+      <c r="J1531">
+        <v>58853</v>
+      </c>
+      <c r="K1531">
+        <v>11</v>
+      </c>
+      <c r="O1531">
+        <v>23</v>
+      </c>
+      <c r="AB1531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1532">
+        <v>12131</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C1532">
+        <v>2206</v>
+      </c>
+      <c r="D1532">
+        <v>20514</v>
+      </c>
+      <c r="E1532">
+        <v>2</v>
+      </c>
+      <c r="F1532">
+        <v>51</v>
+      </c>
+      <c r="G1532" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1532" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1532">
+        <v>21</v>
+      </c>
+      <c r="J1532">
+        <v>58856</v>
+      </c>
+      <c r="K1532">
+        <v>3</v>
+      </c>
+      <c r="O1532" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1533">
+        <v>12132</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C1533">
+        <v>2516</v>
+      </c>
+      <c r="D1533">
+        <v>20502</v>
+      </c>
+      <c r="E1533">
+        <v>8</v>
+      </c>
+      <c r="F1533">
+        <v>52</v>
+      </c>
+      <c r="G1533" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1533" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1533">
+        <v>21</v>
+      </c>
+      <c r="J1533">
+        <v>58857</v>
+      </c>
+      <c r="K1533">
+        <v>1</v>
+      </c>
+      <c r="O1533" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1533" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1534">
+        <v>12143</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C1534">
+        <v>2501</v>
+      </c>
+      <c r="E1534">
+        <v>0</v>
+      </c>
+      <c r="F1534">
+        <v>36</v>
+      </c>
+      <c r="G1534" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1534" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1534">
+        <v>21</v>
+      </c>
+      <c r="J1534">
+        <v>58927</v>
+      </c>
+      <c r="K1534">
+        <v>2</v>
+      </c>
+      <c r="AB1534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1535">
+        <v>12152</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C1535">
+        <v>2501</v>
+      </c>
+      <c r="D1535">
+        <v>20315</v>
+      </c>
+      <c r="E1535">
+        <v>2</v>
+      </c>
+      <c r="F1535">
+        <v>42</v>
+      </c>
+      <c r="G1535" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1535" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1535">
+        <v>22</v>
+      </c>
+      <c r="J1535">
+        <v>58976</v>
+      </c>
+      <c r="K1535">
+        <v>2</v>
+      </c>
+      <c r="AB1535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1536">
+        <v>12152</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C1536">
+        <v>2501</v>
+      </c>
+      <c r="D1536">
+        <v>20315</v>
+      </c>
+      <c r="E1536">
+        <v>2</v>
+      </c>
+      <c r="F1536">
+        <v>42</v>
+      </c>
+      <c r="G1536" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1536" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1536">
+        <v>22</v>
+      </c>
+      <c r="J1536">
+        <v>58977</v>
+      </c>
+      <c r="K1536">
+        <v>3</v>
+      </c>
+      <c r="O1536" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1536">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1537">
+        <v>12155</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C1537">
+        <v>2501</v>
+      </c>
+      <c r="D1537">
+        <v>20315</v>
+      </c>
+      <c r="E1537">
+        <v>2</v>
+      </c>
+      <c r="F1537">
+        <v>45</v>
+      </c>
+      <c r="G1537" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1537" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1537">
+        <v>22</v>
+      </c>
+      <c r="J1537">
+        <v>58985</v>
+      </c>
+      <c r="K1537">
+        <v>2</v>
+      </c>
+      <c r="O1537">
+        <v>21</v>
+      </c>
+      <c r="AB1537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1538">
+        <v>12160</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1538">
+        <v>2616</v>
+      </c>
+      <c r="D1538">
+        <v>20501</v>
+      </c>
+      <c r="E1538">
+        <v>1</v>
+      </c>
+      <c r="F1538">
+        <v>58</v>
+      </c>
+      <c r="G1538" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1538" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1538">
+        <v>22</v>
+      </c>
+      <c r="J1538">
+        <v>59013</v>
+      </c>
+      <c r="K1538">
+        <v>1</v>
+      </c>
+      <c r="AA1538">
+        <v>142</v>
+      </c>
+      <c r="AB1538">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1539">
+        <v>12162</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C1539">
+        <v>2616</v>
+      </c>
+      <c r="D1539">
+        <v>20501</v>
+      </c>
+      <c r="E1539">
+        <v>1</v>
+      </c>
+      <c r="F1539">
+        <v>59</v>
+      </c>
+      <c r="G1539" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1539" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1539">
+        <v>22</v>
+      </c>
+      <c r="J1539">
+        <v>59022</v>
+      </c>
+      <c r="K1539">
+        <v>3</v>
+      </c>
+      <c r="O1539" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1539">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1540">
+        <v>12173</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1540">
+        <v>2616</v>
+      </c>
+      <c r="D1540">
+        <v>20501</v>
+      </c>
+      <c r="E1540">
+        <v>1</v>
+      </c>
+      <c r="F1540">
+        <v>59</v>
+      </c>
+      <c r="G1540" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1540" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1540">
+        <v>23</v>
+      </c>
+      <c r="J1540">
+        <v>59078</v>
+      </c>
+      <c r="K1540">
+        <v>3</v>
+      </c>
+      <c r="O1540" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB1540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1541">
+        <v>12174</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1541">
+        <v>2616</v>
+      </c>
+      <c r="D1541">
+        <v>20501</v>
+      </c>
+      <c r="E1541">
+        <v>1</v>
+      </c>
+      <c r="F1541">
+        <v>60</v>
+      </c>
+      <c r="G1541" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1541" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1541">
+        <v>23</v>
+      </c>
+      <c r="J1541">
+        <v>59091</v>
+      </c>
+      <c r="K1541">
+        <v>12</v>
+      </c>
+      <c r="AB1541">
+        <v>96</v>
+      </c>
+      <c r="AC1541" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1542">
+        <v>12187</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C1542">
+        <v>3604</v>
+      </c>
+      <c r="E1542">
+        <v>0</v>
+      </c>
+      <c r="F1542">
+        <v>71</v>
+      </c>
+      <c r="G1542" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1542" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1542">
+        <v>91</v>
+      </c>
+      <c r="J1542">
+        <v>59140</v>
+      </c>
+      <c r="K1542">
+        <v>2</v>
+      </c>
+      <c r="O1542" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1542">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1543">
+        <v>12194</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C1543">
+        <v>7202</v>
+      </c>
+      <c r="D1543">
+        <v>70210</v>
+      </c>
+      <c r="E1543">
+        <v>7</v>
+      </c>
+      <c r="F1543">
+        <v>5</v>
+      </c>
+      <c r="G1543" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1543" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1543">
+        <v>74</v>
+      </c>
+      <c r="J1543">
+        <v>59166</v>
+      </c>
+      <c r="K1543">
+        <v>2</v>
+      </c>
+      <c r="N1543" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1543">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1544">
+        <v>12203</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C1544">
+        <v>7103</v>
+      </c>
+      <c r="D1544">
+        <v>70403</v>
+      </c>
+      <c r="E1544">
+        <v>7</v>
+      </c>
+      <c r="F1544">
+        <v>23</v>
+      </c>
+      <c r="G1544" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1544" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1544">
+        <v>74</v>
+      </c>
+      <c r="J1544">
+        <v>59202</v>
+      </c>
+      <c r="K1544">
+        <v>1</v>
+      </c>
+      <c r="AA1544" t="s">
+        <v>1423</v>
+      </c>
+      <c r="AB1544">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1545">
+        <v>12203</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C1545">
+        <v>7103</v>
+      </c>
+      <c r="D1545">
+        <v>70403</v>
+      </c>
+      <c r="E1545">
+        <v>7</v>
+      </c>
+      <c r="F1545">
+        <v>23</v>
+      </c>
+      <c r="G1545" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1545" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1545">
+        <v>74</v>
+      </c>
+      <c r="J1545">
+        <v>59203</v>
+      </c>
+      <c r="K1545">
+        <v>2</v>
+      </c>
+      <c r="AA1545" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1545">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1546">
+        <v>12204</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C1546">
+        <v>7203</v>
+      </c>
+      <c r="D1546">
+        <v>70403</v>
+      </c>
+      <c r="E1546">
+        <v>7</v>
+      </c>
+      <c r="F1546">
+        <v>26</v>
+      </c>
+      <c r="G1546" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1546" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1546">
+        <v>74</v>
+      </c>
+      <c r="J1546">
+        <v>59207</v>
+      </c>
+      <c r="K1546">
+        <v>2</v>
+      </c>
+      <c r="T1546">
+        <v>74</v>
+      </c>
+      <c r="AA1546" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1547">
+        <v>12207</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C1547">
+        <v>7102</v>
+      </c>
+      <c r="D1547">
+        <v>70210</v>
+      </c>
+      <c r="E1547">
+        <v>6</v>
+      </c>
+      <c r="F1547">
+        <v>17</v>
+      </c>
+      <c r="G1547" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1547" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1547">
+        <v>73</v>
+      </c>
+      <c r="J1547">
+        <v>59220</v>
+      </c>
+      <c r="K1547">
+        <v>4</v>
+      </c>
+      <c r="AB1547">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1548">
+        <v>12210</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1548">
+        <v>3504</v>
+      </c>
+      <c r="D1548">
+        <v>30602</v>
+      </c>
+      <c r="E1548">
+        <v>6</v>
+      </c>
+      <c r="F1548">
+        <v>73</v>
+      </c>
+      <c r="G1548" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1548" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1548">
+        <v>93</v>
+      </c>
+      <c r="J1548">
+        <v>59230</v>
+      </c>
+      <c r="K1548">
+        <v>4</v>
+      </c>
+      <c r="O1548">
+        <v>21</v>
+      </c>
+      <c r="AB1548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1549">
+        <v>12231</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C1549">
+        <v>7103</v>
+      </c>
+      <c r="D1549">
+        <v>70403</v>
+      </c>
+      <c r="E1549">
+        <v>7</v>
+      </c>
+      <c r="F1549">
+        <v>29</v>
+      </c>
+      <c r="G1549" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1549" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1549">
+        <v>71</v>
+      </c>
+      <c r="J1549">
+        <v>59323</v>
+      </c>
+      <c r="K1549">
+        <v>4</v>
+      </c>
+      <c r="O1549">
+        <v>21</v>
+      </c>
+      <c r="AB1549" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1550">
+        <v>12232</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1550">
+        <v>7203</v>
+      </c>
+      <c r="D1550">
+        <v>70403</v>
+      </c>
+      <c r="E1550">
+        <v>7</v>
+      </c>
+      <c r="F1550">
+        <v>30</v>
+      </c>
+      <c r="G1550" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1550" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1550">
+        <v>71</v>
+      </c>
+      <c r="J1550">
+        <v>59328</v>
+      </c>
+      <c r="K1550">
+        <v>5</v>
+      </c>
+      <c r="Q1550">
+        <v>43</v>
+      </c>
+      <c r="AB1550">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1551">
+        <v>12233</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C1551">
+        <v>7104</v>
+      </c>
+      <c r="D1551">
+        <v>70410</v>
+      </c>
+      <c r="E1551">
+        <v>2</v>
+      </c>
+      <c r="F1551">
+        <v>31</v>
+      </c>
+      <c r="G1551" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1551" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1551">
+        <v>71</v>
+      </c>
+      <c r="J1551">
+        <v>59331</v>
+      </c>
+      <c r="K1551">
+        <v>3</v>
+      </c>
+      <c r="AA1551" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AB1551">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1552">
+        <v>12234</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C1552">
+        <v>7204</v>
+      </c>
+      <c r="D1552">
+        <v>70410</v>
+      </c>
+      <c r="E1552">
+        <v>2</v>
+      </c>
+      <c r="F1552">
+        <v>32</v>
+      </c>
+      <c r="G1552" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1552" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1552">
+        <v>71</v>
+      </c>
+      <c r="J1552">
+        <v>59334</v>
+      </c>
+      <c r="K1552">
+        <v>3</v>
+      </c>
+      <c r="AB1552">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1553">
+        <v>12238</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C1553">
+        <v>3631</v>
+      </c>
+      <c r="E1553">
+        <v>0</v>
+      </c>
+      <c r="F1553">
+        <v>30</v>
+      </c>
+      <c r="G1553" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1553" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1553">
+        <v>58</v>
+      </c>
+      <c r="J1553">
+        <v>59346</v>
+      </c>
+      <c r="K1553">
+        <v>1</v>
+      </c>
+      <c r="AB1553">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1554">
+        <v>12239</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C1554">
+        <v>7204</v>
+      </c>
+      <c r="D1554">
+        <v>70410</v>
+      </c>
+      <c r="E1554">
+        <v>2</v>
+      </c>
+      <c r="F1554">
+        <v>33</v>
+      </c>
+      <c r="G1554" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1554" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1554">
+        <v>71</v>
+      </c>
+      <c r="J1554">
+        <v>59351</v>
+      </c>
+      <c r="K1554">
+        <v>2</v>
+      </c>
+      <c r="O1554">
+        <v>21</v>
+      </c>
+      <c r="AB1554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1555">
+        <v>12240</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C1555">
+        <v>2501</v>
+      </c>
+      <c r="D1555">
+        <v>20315</v>
+      </c>
+      <c r="E1555">
+        <v>10</v>
+      </c>
+      <c r="F1555">
+        <v>38</v>
+      </c>
+      <c r="G1555" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1555" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1555">
+        <v>28</v>
+      </c>
+      <c r="J1555">
+        <v>59362</v>
+      </c>
+      <c r="K1555">
+        <v>7</v>
+      </c>
+      <c r="O1555" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AB1555">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1556">
+        <v>12241</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C1556">
+        <v>2501</v>
+      </c>
+      <c r="D1556">
+        <v>20315</v>
+      </c>
+      <c r="E1556">
+        <v>10</v>
+      </c>
+      <c r="F1556">
+        <v>39</v>
+      </c>
+      <c r="G1556" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1556" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1556">
+        <v>28</v>
+      </c>
+      <c r="J1556">
+        <v>59364</v>
+      </c>
+      <c r="K1556">
+        <v>2</v>
+      </c>
+      <c r="O1556" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AB1556">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1557">
+        <v>12241</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C1557">
+        <v>2501</v>
+      </c>
+      <c r="D1557">
+        <v>20315</v>
+      </c>
+      <c r="E1557">
+        <v>10</v>
+      </c>
+      <c r="F1557">
+        <v>39</v>
+      </c>
+      <c r="G1557" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1557" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1557">
+        <v>28</v>
+      </c>
+      <c r="J1557">
+        <v>59366</v>
+      </c>
+      <c r="K1557">
+        <v>4</v>
+      </c>
+      <c r="O1557" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AB1557">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1558">
+        <v>12247</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C1558">
+        <v>7104</v>
+      </c>
+      <c r="D1558">
+        <v>70410</v>
+      </c>
+      <c r="E1558">
+        <v>2</v>
+      </c>
+      <c r="F1558">
+        <v>37</v>
+      </c>
+      <c r="G1558" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1558" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1558">
+        <v>72</v>
+      </c>
+      <c r="J1558">
+        <v>59408</v>
+      </c>
+      <c r="K1558">
+        <v>9</v>
+      </c>
+      <c r="O1558">
+        <v>21</v>
+      </c>
+      <c r="AB1558">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1559">
+        <v>12252</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C1559">
+        <v>7204</v>
+      </c>
+      <c r="D1559">
+        <v>70410</v>
+      </c>
+      <c r="E1559">
+        <v>2</v>
+      </c>
+      <c r="F1559">
+        <v>32</v>
+      </c>
+      <c r="G1559" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1559" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1559">
+        <v>72</v>
+      </c>
+      <c r="J1559">
+        <v>59433</v>
+      </c>
+      <c r="K1559">
+        <v>4</v>
+      </c>
+      <c r="AB1559">
+        <v>1</v>
+      </c>
+      <c r="AC1559" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1560">
+        <v>12254</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C1560">
+        <v>7305</v>
+      </c>
+      <c r="D1560">
+        <v>70502</v>
+      </c>
+      <c r="E1560">
+        <v>5</v>
+      </c>
+      <c r="F1560">
+        <v>44</v>
+      </c>
+      <c r="G1560" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1560" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1560">
+        <v>72</v>
+      </c>
+      <c r="J1560">
+        <v>59443</v>
+      </c>
+      <c r="K1560">
+        <v>4</v>
+      </c>
+      <c r="AB1560">
+        <v>1</v>
+      </c>
+      <c r="AC1560" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1561">
+        <v>12257</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1561">
+        <v>7204</v>
+      </c>
+      <c r="D1561">
+        <v>70410</v>
+      </c>
+      <c r="E1561">
+        <v>2</v>
+      </c>
+      <c r="F1561">
+        <v>36</v>
+      </c>
+      <c r="G1561" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1561" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1561">
+        <v>71</v>
+      </c>
+      <c r="J1561">
+        <v>59457</v>
+      </c>
+      <c r="K1561">
+        <v>3</v>
+      </c>
+      <c r="AB1561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1562">
+        <v>12258</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C1562">
+        <v>7104</v>
+      </c>
+      <c r="D1562">
+        <v>70410</v>
+      </c>
+      <c r="E1562">
+        <v>2</v>
+      </c>
+      <c r="F1562">
+        <v>35</v>
+      </c>
+      <c r="G1562" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1562" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1562">
+        <v>71</v>
+      </c>
+      <c r="J1562">
+        <v>59463</v>
+      </c>
+      <c r="K1562">
+        <v>2</v>
+      </c>
+      <c r="AB1562" t="s">
+        <v>558</v>
+      </c>
+      <c r="AC1562" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1563">
+        <v>13503</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1563">
+        <v>2106</v>
+      </c>
+      <c r="D1563">
+        <v>20514</v>
+      </c>
+      <c r="E1563">
+        <v>2</v>
+      </c>
+      <c r="F1563">
+        <v>44</v>
+      </c>
+      <c r="G1563" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1563" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1563">
+        <v>28</v>
+      </c>
+      <c r="J1563">
+        <v>5948337</v>
+      </c>
+      <c r="K1563">
+        <v>7</v>
+      </c>
+      <c r="Y1563" t="s">
+        <v>1446</v>
+      </c>
+      <c r="AB1563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1564">
+        <v>13507</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1564">
+        <v>1401</v>
+      </c>
+      <c r="D1564">
+        <v>31304</v>
+      </c>
+      <c r="E1564">
+        <v>4</v>
+      </c>
+      <c r="F1564">
+        <v>42</v>
+      </c>
+      <c r="G1564" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1564" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1564">
+        <v>51</v>
+      </c>
+      <c r="J1564">
+        <v>5948358</v>
+      </c>
+      <c r="K1564">
+        <v>1</v>
+      </c>
+      <c r="O1564">
+        <v>23</v>
+      </c>
+      <c r="AB1564">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1565">
+        <v>13508</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C1565">
+        <v>3416</v>
+      </c>
+      <c r="D1565">
+        <v>30802</v>
+      </c>
+      <c r="E1565">
+        <v>4</v>
+      </c>
+      <c r="F1565">
+        <v>43</v>
+      </c>
+      <c r="G1565" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1565" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1565">
+        <v>51</v>
+      </c>
+      <c r="J1565">
+        <v>5948361</v>
+      </c>
+      <c r="K1565">
+        <v>1</v>
+      </c>
+      <c r="AB1565">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1566">
+        <v>13510</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C1566">
+        <v>3470</v>
+      </c>
+      <c r="D1566">
+        <v>30605</v>
+      </c>
+      <c r="E1566">
+        <v>8</v>
+      </c>
+      <c r="F1566">
+        <v>45</v>
+      </c>
+      <c r="G1566" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1566" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1566">
+        <v>51</v>
+      </c>
+      <c r="J1566">
+        <v>5948377</v>
+      </c>
+      <c r="K1566">
+        <v>4</v>
+      </c>
+      <c r="AB1566">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1567">
+        <v>13512</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C1567">
+        <v>3470</v>
+      </c>
+      <c r="D1567">
+        <v>30605</v>
+      </c>
+      <c r="E1567">
+        <v>8</v>
+      </c>
+      <c r="F1567">
+        <v>47</v>
+      </c>
+      <c r="G1567" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1567" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1567">
+        <v>51</v>
+      </c>
+      <c r="J1567">
+        <v>5948386</v>
+      </c>
+      <c r="K1567">
+        <v>3</v>
+      </c>
+      <c r="AB1567">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1568">
+        <v>13512</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C1568">
+        <v>3470</v>
+      </c>
+      <c r="D1568">
+        <v>30605</v>
+      </c>
+      <c r="E1568">
+        <v>8</v>
+      </c>
+      <c r="F1568">
+        <v>47</v>
+      </c>
+      <c r="G1568" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1568" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1568">
+        <v>51</v>
+      </c>
+      <c r="J1568">
+        <v>5948387</v>
+      </c>
+      <c r="K1568">
+        <v>4</v>
+      </c>
+      <c r="AB1568">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1569">
+        <v>13521</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C1569">
+        <v>1416</v>
+      </c>
+      <c r="D1569">
+        <v>11101</v>
+      </c>
+      <c r="E1569">
+        <v>6</v>
+      </c>
+      <c r="F1569">
+        <v>74</v>
+      </c>
+      <c r="G1569" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1569" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1569">
+        <v>13</v>
+      </c>
+      <c r="J1569">
+        <v>5948433</v>
+      </c>
+      <c r="K1569">
+        <v>1</v>
+      </c>
+      <c r="U1569">
+        <v>81</v>
+      </c>
+      <c r="AB1569">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1570">
+        <v>13539</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C1570">
+        <v>1416</v>
+      </c>
+      <c r="D1570">
+        <v>11101</v>
+      </c>
+      <c r="E1570">
+        <v>6</v>
+      </c>
+      <c r="F1570">
+        <v>74</v>
+      </c>
+      <c r="G1570" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1570" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1570">
+        <v>14</v>
+      </c>
+      <c r="J1570">
+        <v>5948523</v>
+      </c>
+      <c r="K1570">
+        <v>1</v>
+      </c>
+      <c r="O1570">
+        <v>21</v>
+      </c>
+      <c r="AB1570">
+        <v>1</v>
+      </c>
+      <c r="AC1570" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1571">
+        <v>13554</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C1571">
+        <v>3115</v>
+      </c>
+      <c r="D1571">
+        <v>31304</v>
+      </c>
+      <c r="E1571">
+        <v>4</v>
+      </c>
+      <c r="F1571">
+        <v>12</v>
+      </c>
+      <c r="G1571" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1571" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1571">
+        <v>51</v>
+      </c>
+      <c r="J1571">
+        <v>5948603</v>
+      </c>
+      <c r="K1571">
+        <v>2</v>
+      </c>
+      <c r="O1571">
+        <v>21</v>
+      </c>
+      <c r="AB1571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1572">
+        <v>13556</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C1572">
+        <v>3473</v>
+      </c>
+      <c r="D1572">
+        <v>30802</v>
+      </c>
+      <c r="E1572">
+        <v>5</v>
+      </c>
+      <c r="F1572">
+        <v>3</v>
+      </c>
+      <c r="G1572" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1572" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1572">
+        <v>53</v>
+      </c>
+      <c r="J1572">
+        <v>5948608</v>
+      </c>
+      <c r="K1572">
+        <v>1</v>
+      </c>
+      <c r="O1572">
+        <v>21</v>
+      </c>
+      <c r="AB1572">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1573">
+        <v>13561</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C1573">
+        <v>3470</v>
+      </c>
+      <c r="D1573">
+        <v>30605</v>
+      </c>
+      <c r="E1573">
+        <v>8</v>
+      </c>
+      <c r="F1573">
+        <v>8</v>
+      </c>
+      <c r="G1573" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1573" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1573">
+        <v>53</v>
+      </c>
+      <c r="J1573">
+        <v>5948631</v>
+      </c>
+      <c r="K1573">
+        <v>3</v>
+      </c>
+      <c r="AB1573">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1574">
+        <v>13561</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C1574">
+        <v>3470</v>
+      </c>
+      <c r="D1574">
+        <v>30605</v>
+      </c>
+      <c r="E1574">
+        <v>8</v>
+      </c>
+      <c r="F1574">
+        <v>8</v>
+      </c>
+      <c r="G1574" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1574" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1574">
+        <v>53</v>
+      </c>
+      <c r="J1574">
+        <v>5948632</v>
+      </c>
+      <c r="K1574">
+        <v>4</v>
+      </c>
+      <c r="AB1574">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1575">
+        <v>13561</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C1575">
+        <v>3470</v>
+      </c>
+      <c r="D1575">
+        <v>30605</v>
+      </c>
+      <c r="E1575">
+        <v>8</v>
+      </c>
+      <c r="F1575">
+        <v>8</v>
+      </c>
+      <c r="G1575" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1575" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1575">
+        <v>53</v>
+      </c>
+      <c r="J1575">
+        <v>5948633</v>
+      </c>
+      <c r="K1575">
+        <v>5</v>
+      </c>
+      <c r="AB1575">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1576">
+        <v>13566</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C1576">
+        <v>3416</v>
+      </c>
+      <c r="D1576">
+        <v>30608</v>
+      </c>
+      <c r="E1576">
+        <v>28</v>
+      </c>
+      <c r="F1576">
+        <v>13</v>
+      </c>
+      <c r="G1576" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1576" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1576">
+        <v>53</v>
+      </c>
+      <c r="J1576">
+        <v>5948652</v>
+      </c>
+      <c r="K1576">
+        <v>2</v>
+      </c>
+      <c r="U1576">
+        <v>81</v>
+      </c>
+      <c r="AB1576">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1577">
+        <v>13568</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C1577">
+        <v>2206</v>
+      </c>
+      <c r="D1577">
+        <v>20514</v>
+      </c>
+      <c r="E1577">
+        <v>8</v>
+      </c>
+      <c r="F1577">
+        <v>46</v>
+      </c>
+      <c r="G1577" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1577" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1577">
+        <v>28</v>
+      </c>
+      <c r="J1577">
+        <v>5948664</v>
+      </c>
+      <c r="K1577">
+        <v>3</v>
+      </c>
+      <c r="O1577" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AB1577">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1578">
+        <v>13572</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C1578">
+        <v>2106</v>
+      </c>
+      <c r="D1578">
+        <v>20514</v>
+      </c>
+      <c r="E1578">
+        <v>6</v>
+      </c>
+      <c r="F1578">
+        <v>46</v>
+      </c>
+      <c r="G1578" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1578" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1578">
+        <v>24</v>
+      </c>
+      <c r="J1578">
+        <v>5948690</v>
+      </c>
+      <c r="K1578">
+        <v>11</v>
+      </c>
+      <c r="O1578">
+        <v>21</v>
+      </c>
+      <c r="AB1578">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1579">
+        <v>13591</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C1579">
+        <v>3625</v>
+      </c>
+      <c r="D1579">
+        <v>30608</v>
+      </c>
+      <c r="E1579">
+        <v>13</v>
+      </c>
+      <c r="F1579">
+        <v>88</v>
+      </c>
+      <c r="G1579" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1579" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1579">
+        <v>93</v>
+      </c>
+      <c r="J1579">
+        <v>5948786</v>
+      </c>
+      <c r="K1579">
+        <v>4</v>
+      </c>
+      <c r="O1579">
+        <v>21</v>
+      </c>
+      <c r="AB1579">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1580">
+        <v>13596</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C1580">
+        <v>2206</v>
+      </c>
+      <c r="D1580">
+        <v>20514</v>
+      </c>
+      <c r="E1580">
+        <v>6</v>
+      </c>
+      <c r="F1580">
+        <v>47</v>
+      </c>
+      <c r="G1580" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1580" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1580">
+        <v>28</v>
+      </c>
+      <c r="J1580">
+        <v>5948809</v>
+      </c>
+      <c r="K1580">
+        <v>6</v>
+      </c>
+      <c r="AB1580">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1581">
+        <v>13598</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C1581">
+        <v>2616</v>
+      </c>
+      <c r="D1581">
+        <v>20502</v>
+      </c>
+      <c r="E1581">
+        <v>2</v>
+      </c>
+      <c r="F1581">
+        <v>49</v>
+      </c>
+      <c r="G1581" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1581" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1581">
+        <v>28</v>
+      </c>
+      <c r="J1581">
+        <v>5948818</v>
+      </c>
+      <c r="K1581">
+        <v>4</v>
+      </c>
+      <c r="AB1581">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1582">
+        <v>13599</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1582">
+        <v>2616</v>
+      </c>
+      <c r="D1582">
+        <v>20501</v>
+      </c>
+      <c r="E1582">
+        <v>1</v>
+      </c>
+      <c r="F1582">
+        <v>50</v>
+      </c>
+      <c r="G1582" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1582" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1582">
+        <v>28</v>
+      </c>
+      <c r="J1582">
+        <v>5948825</v>
+      </c>
+      <c r="K1582">
+        <v>7</v>
+      </c>
+      <c r="AB1582">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1583">
+        <v>13613</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C1583">
+        <v>3617</v>
+      </c>
+      <c r="D1583">
+        <v>30608</v>
+      </c>
+      <c r="E1583">
+        <v>10</v>
+      </c>
+      <c r="F1583">
+        <v>84</v>
+      </c>
+      <c r="G1583" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1583" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1583">
+        <v>13</v>
+      </c>
+      <c r="J1583">
+        <v>5948876</v>
+      </c>
+      <c r="K1583">
+        <v>1</v>
+      </c>
+      <c r="N1583">
+        <v>11</v>
+      </c>
+      <c r="AB1583">
+        <v>1</v>
+      </c>
+      <c r="AC1583" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1584">
+        <v>13615</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C1584">
+        <v>3504</v>
+      </c>
+      <c r="D1584">
+        <v>30603</v>
+      </c>
+      <c r="E1584">
+        <v>6</v>
+      </c>
+      <c r="F1584">
+        <v>80</v>
+      </c>
+      <c r="G1584" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1584" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1584">
+        <v>94</v>
+      </c>
+      <c r="J1584">
+        <v>5948887</v>
+      </c>
+      <c r="K1584">
+        <v>2</v>
+      </c>
+      <c r="U1584">
+        <v>82</v>
+      </c>
+      <c r="AB1584">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1585">
+        <v>13617</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C1585">
+        <v>3633</v>
+      </c>
+      <c r="E1585">
+        <v>0</v>
+      </c>
+      <c r="F1585">
+        <v>77</v>
+      </c>
+      <c r="G1585" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1585" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1585">
+        <v>57</v>
+      </c>
+      <c r="J1585">
+        <v>5948893</v>
+      </c>
+      <c r="K1585">
+        <v>3</v>
+      </c>
+      <c r="AB1585">
+        <v>96</v>
+      </c>
+      <c r="AC1585" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1586">
+        <v>13620</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C1586">
+        <v>3382</v>
+      </c>
+      <c r="D1586">
+        <v>30802</v>
+      </c>
+      <c r="E1586">
+        <v>3</v>
+      </c>
+      <c r="F1586">
+        <v>21</v>
+      </c>
+      <c r="G1586" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1586" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1586">
+        <v>57</v>
+      </c>
+      <c r="J1586">
+        <v>5948905</v>
+      </c>
+      <c r="K1586">
+        <v>4</v>
+      </c>
+      <c r="Q1586" t="s">
+        <v>1469</v>
+      </c>
+      <c r="AB1586">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1587">
+        <v>13621</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C1587">
+        <v>3630</v>
+      </c>
+      <c r="E1587">
+        <v>0</v>
+      </c>
+      <c r="F1587">
+        <v>22</v>
+      </c>
+      <c r="G1587" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1587" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1587">
+        <v>57</v>
+      </c>
+      <c r="J1587">
+        <v>5948910</v>
+      </c>
+      <c r="K1587">
+        <v>5</v>
+      </c>
+      <c r="X1587">
+        <v>111</v>
+      </c>
+      <c r="AB1587">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1588">
+        <v>13630</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C1588">
+        <v>3549</v>
+      </c>
+      <c r="E1588">
+        <v>0</v>
+      </c>
+      <c r="F1588">
+        <v>39</v>
+      </c>
+      <c r="G1588" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1588" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1588">
+        <v>56</v>
+      </c>
+      <c r="J1588">
+        <v>5948946</v>
+      </c>
+      <c r="K1588">
+        <v>2</v>
+      </c>
+      <c r="O1588">
+        <v>21</v>
+      </c>
+      <c r="AB1588">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1589">
+        <v>13644</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C1589">
+        <v>7203</v>
+      </c>
+      <c r="D1589">
+        <v>70403</v>
+      </c>
+      <c r="E1589">
+        <v>7</v>
+      </c>
+      <c r="F1589">
+        <v>19</v>
+      </c>
+      <c r="G1589" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1589" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1589">
+        <v>74</v>
+      </c>
+      <c r="J1589">
+        <v>5949009</v>
+      </c>
+      <c r="K1589">
+        <v>2</v>
+      </c>
+      <c r="AC1589" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1590">
+        <v>13645</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C1590">
+        <v>7103</v>
+      </c>
+      <c r="D1590">
+        <v>70403</v>
+      </c>
+      <c r="E1590">
+        <v>7</v>
+      </c>
+      <c r="F1590">
+        <v>18</v>
+      </c>
+      <c r="G1590" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1590" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1590">
+        <v>74</v>
+      </c>
+      <c r="J1590">
+        <v>5949013</v>
+      </c>
+      <c r="K1590">
+        <v>2</v>
+      </c>
+      <c r="AB1590">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1591">
+        <v>13646</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C1591">
+        <v>6310</v>
+      </c>
+      <c r="D1591">
+        <v>61006</v>
+      </c>
+      <c r="E1591">
+        <v>1</v>
+      </c>
+      <c r="F1591">
+        <v>42</v>
+      </c>
+      <c r="G1591" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1591" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1591">
+        <v>71</v>
+      </c>
+      <c r="J1591">
+        <v>5949018</v>
+      </c>
+      <c r="K1591">
+        <v>2</v>
+      </c>
+      <c r="AB1591">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1592">
+        <v>13647</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C1592">
+        <v>6310</v>
+      </c>
+      <c r="D1592">
+        <v>61006</v>
+      </c>
+      <c r="E1592">
+        <v>1</v>
+      </c>
+      <c r="F1592">
+        <v>41</v>
+      </c>
+      <c r="G1592" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1592" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1592">
+        <v>71</v>
+      </c>
+      <c r="J1592">
+        <v>5949020</v>
+      </c>
+      <c r="K1592">
+        <v>1</v>
+      </c>
+      <c r="AB1592">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1593">
+        <v>13662</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C1593">
+        <v>3617</v>
+      </c>
+      <c r="D1593">
+        <v>30608</v>
+      </c>
+      <c r="E1593">
+        <v>10</v>
+      </c>
+      <c r="F1593">
+        <v>82</v>
+      </c>
+      <c r="G1593" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1593" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1593">
+        <v>14</v>
+      </c>
+      <c r="J1593">
+        <v>5949077</v>
+      </c>
+      <c r="K1593">
+        <v>1</v>
+      </c>
+      <c r="AB1593">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1594">
+        <v>13671</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C1594">
+        <v>3414</v>
+      </c>
+      <c r="D1594">
+        <v>31206</v>
+      </c>
+      <c r="E1594">
+        <v>8</v>
+      </c>
+      <c r="F1594">
+        <v>71</v>
+      </c>
+      <c r="G1594" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1594" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1594">
+        <v>22</v>
+      </c>
+      <c r="J1594">
+        <v>5949122</v>
+      </c>
+      <c r="K1594">
+        <v>1</v>
+      </c>
+      <c r="U1594">
+        <v>81</v>
+      </c>
+      <c r="AB1594">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1595">
+        <v>13672</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C1595">
+        <v>3414</v>
+      </c>
+      <c r="D1595">
+        <v>31206</v>
+      </c>
+      <c r="E1595">
+        <v>8</v>
+      </c>
+      <c r="F1595">
+        <v>70</v>
+      </c>
+      <c r="G1595" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1595" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1595">
+        <v>22</v>
+      </c>
+      <c r="J1595">
+        <v>5949127</v>
+      </c>
+      <c r="K1595">
+        <v>2</v>
+      </c>
+      <c r="U1595" t="s">
+        <v>1480</v>
+      </c>
+      <c r="AB1595">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1596">
+        <v>13675</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C1596">
+        <v>3410</v>
+      </c>
+      <c r="D1596">
+        <v>31206</v>
+      </c>
+      <c r="E1596">
+        <v>8</v>
+      </c>
+      <c r="F1596">
+        <v>67</v>
+      </c>
+      <c r="G1596" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1596" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1596">
+        <v>22</v>
+      </c>
+      <c r="J1596">
+        <v>5949138</v>
+      </c>
+      <c r="K1596">
+        <v>4</v>
+      </c>
+      <c r="O1596" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1596">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1597">
+        <v>13678</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C1597">
+        <v>3310</v>
+      </c>
+      <c r="D1597">
+        <v>31206</v>
+      </c>
+      <c r="E1597">
+        <v>8</v>
+      </c>
+      <c r="F1597">
+        <v>64</v>
+      </c>
+      <c r="G1597" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1597" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1597">
+        <v>22</v>
+      </c>
+      <c r="J1597">
+        <v>5949147</v>
+      </c>
+      <c r="K1597">
+        <v>2</v>
+      </c>
+      <c r="AA1597">
+        <v>142</v>
+      </c>
+      <c r="AB1597">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1598">
+        <v>13683</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C1598">
+        <v>6316</v>
+      </c>
+      <c r="D1598">
+        <v>61006</v>
+      </c>
+      <c r="E1598">
+        <v>4</v>
+      </c>
+      <c r="F1598">
+        <v>45</v>
+      </c>
+      <c r="G1598" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1598" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1598">
+        <v>71</v>
+      </c>
+      <c r="J1598">
+        <v>5949171</v>
+      </c>
+      <c r="K1598">
+        <v>3</v>
+      </c>
+      <c r="O1598">
+        <v>21</v>
+      </c>
+      <c r="AB1598">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1599">
+        <v>13684</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C1599">
+        <v>2616</v>
+      </c>
+      <c r="D1599">
+        <v>20501</v>
+      </c>
+      <c r="E1599">
+        <v>1</v>
+      </c>
+      <c r="F1599">
+        <v>53</v>
+      </c>
+      <c r="G1599" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1599" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1599">
+        <v>28</v>
+      </c>
+      <c r="J1599">
+        <v>5949172</v>
+      </c>
+      <c r="K1599">
+        <v>1</v>
+      </c>
+      <c r="AB1599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1600">
+        <v>13687</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C1600">
+        <v>3310</v>
+      </c>
+      <c r="D1600">
+        <v>31206</v>
+      </c>
+      <c r="E1600">
+        <v>8</v>
+      </c>
+      <c r="F1600">
+        <v>55</v>
+      </c>
+      <c r="G1600" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1600" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1600">
+        <v>28</v>
+      </c>
+      <c r="J1600">
+        <v>5949185</v>
+      </c>
+      <c r="K1600">
+        <v>1</v>
+      </c>
+      <c r="AB1600">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1601">
+        <v>13691</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1601">
+        <v>3410</v>
+      </c>
+      <c r="D1601">
+        <v>31206</v>
+      </c>
+      <c r="E1601">
+        <v>8</v>
+      </c>
+      <c r="F1601">
+        <v>59</v>
+      </c>
+      <c r="G1601" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1601" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1601">
+        <v>28</v>
+      </c>
+      <c r="J1601">
+        <v>5949204</v>
+      </c>
+      <c r="K1601">
+        <v>1</v>
+      </c>
+      <c r="AB1601">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1602">
+        <v>13691</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1602">
+        <v>3410</v>
+      </c>
+      <c r="D1602">
+        <v>31206</v>
+      </c>
+      <c r="E1602">
+        <v>8</v>
+      </c>
+      <c r="F1602">
+        <v>59</v>
+      </c>
+      <c r="G1602" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1602" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1602">
+        <v>28</v>
+      </c>
+      <c r="J1602">
+        <v>5949206</v>
+      </c>
+      <c r="K1602">
+        <v>3</v>
+      </c>
+      <c r="AB1602">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1603">
+        <v>13697</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C1603">
+        <v>3581</v>
+      </c>
+      <c r="D1603">
+        <v>30608</v>
+      </c>
+      <c r="E1603">
+        <v>9</v>
+      </c>
+      <c r="F1603">
+        <v>96</v>
+      </c>
+      <c r="G1603" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1603" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1603">
+        <v>93</v>
+      </c>
+      <c r="J1603">
+        <v>5949234</v>
+      </c>
+      <c r="K1603">
+        <v>1</v>
+      </c>
+      <c r="O1603">
+        <v>21</v>
+      </c>
+      <c r="AB1603">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1604">
+        <v>13698</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C1604">
+        <v>3677</v>
+      </c>
+      <c r="D1604">
+        <v>30608</v>
+      </c>
+      <c r="E1604">
+        <v>11</v>
+      </c>
+      <c r="F1604">
+        <v>95</v>
+      </c>
+      <c r="G1604" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1604" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1604">
+        <v>93</v>
+      </c>
+      <c r="J1604">
+        <v>5949239</v>
+      </c>
+      <c r="K1604">
+        <v>3</v>
+      </c>
+      <c r="AA1604">
+        <v>141</v>
+      </c>
+      <c r="AB1604">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1605">
+        <v>13703</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C1605">
+        <v>2516</v>
+      </c>
+      <c r="D1605">
+        <v>20502</v>
+      </c>
+      <c r="E1605">
+        <v>8</v>
+      </c>
+      <c r="F1605">
+        <v>54</v>
+      </c>
+      <c r="G1605" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1605" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1605">
+        <v>24</v>
+      </c>
+      <c r="J1605">
+        <v>5949268</v>
+      </c>
+      <c r="K1605">
+        <v>7</v>
+      </c>
+      <c r="U1605">
+        <v>82</v>
+      </c>
+      <c r="AB1605">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1606">
+        <v>13714</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C1606">
+        <v>6416</v>
+      </c>
+      <c r="D1606">
+        <v>61006</v>
+      </c>
+      <c r="E1606">
+        <v>4</v>
+      </c>
+      <c r="F1606">
+        <v>49</v>
+      </c>
+      <c r="G1606" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1606" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1606">
+        <v>71</v>
+      </c>
+      <c r="J1606">
+        <v>5949318</v>
+      </c>
+      <c r="K1606">
+        <v>2</v>
+      </c>
+      <c r="AB1606">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1607">
+        <v>13721</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C1607">
+        <v>6408</v>
+      </c>
+      <c r="D1607">
+        <v>60608</v>
+      </c>
+      <c r="E1607">
+        <v>1</v>
+      </c>
+      <c r="F1607">
+        <v>50</v>
+      </c>
+      <c r="G1607" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1607" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1607">
+        <v>71</v>
+      </c>
+      <c r="J1607">
+        <v>5949341</v>
+      </c>
+      <c r="K1607">
+        <v>2</v>
+      </c>
+      <c r="AB1607">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1608">
+        <v>13733</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C1608">
+        <v>3549</v>
+      </c>
+      <c r="D1608">
+        <v>30802</v>
+      </c>
+      <c r="E1608">
+        <v>2</v>
+      </c>
+      <c r="F1608">
+        <v>30</v>
+      </c>
+      <c r="G1608" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1608" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1608">
+        <v>55</v>
+      </c>
+      <c r="J1608">
+        <v>5949381</v>
+      </c>
+      <c r="K1608">
+        <v>1</v>
+      </c>
+      <c r="AB1608">
+        <v>96</v>
+      </c>
+      <c r="AC1608" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1609">
+        <v>13737</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C1609">
+        <v>6416</v>
+      </c>
+      <c r="D1609">
+        <v>61006</v>
+      </c>
+      <c r="E1609">
+        <v>4</v>
+      </c>
+      <c r="F1609">
+        <v>51</v>
+      </c>
+      <c r="G1609" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1609" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1609">
+        <v>71</v>
+      </c>
+      <c r="J1609">
+        <v>5949399</v>
+      </c>
+      <c r="K1609">
+        <v>2</v>
+      </c>
+      <c r="O1609">
+        <v>21</v>
+      </c>
+      <c r="AB1609">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1610">
+        <v>13738</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C1610">
+        <v>3681</v>
+      </c>
+      <c r="D1610">
+        <v>30608</v>
+      </c>
+      <c r="E1610">
+        <v>9</v>
+      </c>
+      <c r="F1610">
+        <v>83</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1610" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1610">
+        <v>94</v>
+      </c>
+      <c r="J1610">
+        <v>5949402</v>
+      </c>
+      <c r="K1610">
+        <v>2</v>
+      </c>
+      <c r="Y1610" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AB1610">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1611">
+        <v>13741</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C1611">
+        <v>3115</v>
+      </c>
+      <c r="D1611">
+        <v>31304</v>
+      </c>
+      <c r="E1611">
+        <v>4</v>
+      </c>
+      <c r="F1611">
+        <v>16</v>
+      </c>
+      <c r="G1611" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1611" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1611">
+        <v>51</v>
+      </c>
+      <c r="J1611">
+        <v>5949421</v>
+      </c>
+      <c r="K1611">
+        <v>3</v>
+      </c>
+      <c r="AB1611">
+        <v>96</v>
+      </c>
+      <c r="AC1611" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1612">
+        <v>13742</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C1612">
+        <v>6410</v>
+      </c>
+      <c r="D1612">
+        <v>61006</v>
+      </c>
+      <c r="E1612">
+        <v>1</v>
+      </c>
+      <c r="F1612">
+        <v>43</v>
+      </c>
+      <c r="G1612" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1612" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1612">
+        <v>71</v>
+      </c>
+      <c r="J1612">
+        <v>5949427</v>
+      </c>
+      <c r="K1612">
+        <v>5</v>
+      </c>
+      <c r="O1612">
+        <v>21</v>
+      </c>
+      <c r="AB1612">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1613">
+        <v>13743</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C1613">
+        <v>3542</v>
+      </c>
+      <c r="D1613">
+        <v>30802</v>
+      </c>
+      <c r="E1613">
+        <v>0</v>
+      </c>
+      <c r="F1613">
+        <v>44</v>
+      </c>
+      <c r="G1613" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1613" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1613">
+        <v>56</v>
+      </c>
+      <c r="J1613">
+        <v>5949431</v>
+      </c>
+      <c r="K1613">
+        <v>4</v>
+      </c>
+      <c r="O1613" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AB1613">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1614">
+        <v>13750</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C1614">
+        <v>3546</v>
+      </c>
+      <c r="E1614">
+        <v>0</v>
+      </c>
+      <c r="F1614">
+        <v>43</v>
+      </c>
+      <c r="G1614" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1614" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1614">
+        <v>85</v>
+      </c>
+      <c r="J1614">
+        <v>5949461</v>
+      </c>
+      <c r="K1614">
+        <v>4</v>
+      </c>
+      <c r="AB1614">
+        <v>1</v>
+      </c>
+      <c r="AC1614" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1615">
+        <v>13761</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1615">
+        <v>3604</v>
+      </c>
+      <c r="E1615">
+        <v>0</v>
+      </c>
+      <c r="F1615">
+        <v>83</v>
+      </c>
+      <c r="G1615" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1615" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1615">
+        <v>91</v>
+      </c>
+      <c r="J1615">
+        <v>5949492</v>
+      </c>
+      <c r="K1615">
+        <v>1</v>
+      </c>
+      <c r="O1615">
+        <v>21</v>
+      </c>
+      <c r="AB1615">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1616">
+        <v>13761</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1616">
+        <v>3604</v>
+      </c>
+      <c r="E1616">
+        <v>0</v>
+      </c>
+      <c r="F1616">
+        <v>83</v>
+      </c>
+      <c r="G1616" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1616" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1616">
+        <v>91</v>
+      </c>
+      <c r="J1616">
+        <v>5949494</v>
+      </c>
+      <c r="K1616">
+        <v>3</v>
+      </c>
+      <c r="O1616">
+        <v>21</v>
+      </c>
+      <c r="AB1616">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1617">
+        <v>13762</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1617">
+        <v>3504</v>
+      </c>
+      <c r="E1617">
+        <v>0</v>
+      </c>
+      <c r="F1617">
+        <v>84</v>
+      </c>
+      <c r="G1617" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1617" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1617">
+        <v>91</v>
+      </c>
+      <c r="J1617">
+        <v>5949499</v>
+      </c>
+      <c r="K1617">
+        <v>3</v>
+      </c>
+      <c r="O1617">
+        <v>21</v>
+      </c>
+      <c r="AB1617">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1618">
+        <v>13762</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1618">
+        <v>3504</v>
+      </c>
+      <c r="E1618">
+        <v>0</v>
+      </c>
+      <c r="F1618">
+        <v>84</v>
+      </c>
+      <c r="G1618" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1618" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1618">
+        <v>91</v>
+      </c>
+      <c r="J1618">
+        <v>5949500</v>
+      </c>
+      <c r="K1618">
+        <v>4</v>
+      </c>
+      <c r="O1618">
+        <v>21</v>
+      </c>
+      <c r="AB1618">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1619">
+        <v>13763</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C1619">
+        <v>3676</v>
+      </c>
+      <c r="E1619">
+        <v>0</v>
+      </c>
+      <c r="F1619">
+        <v>85</v>
+      </c>
+      <c r="G1619" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1619" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1619">
+        <v>91</v>
+      </c>
+      <c r="J1619">
+        <v>5949503</v>
+      </c>
+      <c r="K1619">
+        <v>1</v>
+      </c>
+      <c r="O1619">
+        <v>21</v>
+      </c>
+      <c r="AB1619">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1620">
+        <v>13766</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C1620">
+        <v>3602</v>
+      </c>
+      <c r="E1620">
+        <v>0</v>
+      </c>
+      <c r="F1620">
+        <v>88</v>
+      </c>
+      <c r="G1620" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1620" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1620">
+        <v>91</v>
+      </c>
+      <c r="J1620">
+        <v>5949514</v>
+      </c>
+      <c r="K1620">
+        <v>2</v>
+      </c>
+      <c r="AA1620" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB1620">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1621">
+        <v>13767</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1621">
+        <v>3613</v>
+      </c>
+      <c r="E1621">
+        <v>0</v>
+      </c>
+      <c r="F1621">
+        <v>89</v>
+      </c>
+      <c r="G1621" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1621" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1621">
+        <v>91</v>
+      </c>
+      <c r="J1621">
+        <v>5949517</v>
+      </c>
+      <c r="K1621">
+        <v>3</v>
+      </c>
+      <c r="O1621" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1621">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1622">
+        <v>13769</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C1622">
+        <v>3604</v>
+      </c>
+      <c r="E1622">
+        <v>0</v>
+      </c>
+      <c r="F1622">
+        <v>91</v>
+      </c>
+      <c r="G1622" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1622" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1622">
+        <v>91</v>
+      </c>
+      <c r="J1622">
+        <v>5949523</v>
+      </c>
+      <c r="K1622">
+        <v>1</v>
+      </c>
+      <c r="O1622" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1622">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1623">
+        <v>13770</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C1623">
+        <v>3602</v>
+      </c>
+      <c r="E1623">
+        <v>0</v>
+      </c>
+      <c r="F1623">
+        <v>92</v>
+      </c>
+      <c r="G1623" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1623" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1623">
+        <v>91</v>
+      </c>
+      <c r="J1623">
+        <v>5949527</v>
+      </c>
+      <c r="K1623">
+        <v>3</v>
+      </c>
+      <c r="O1623" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1623">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1624">
+        <v>13771</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C1624">
+        <v>3504</v>
+      </c>
+      <c r="E1624">
+        <v>0</v>
+      </c>
+      <c r="F1624">
+        <v>93</v>
+      </c>
+      <c r="G1624" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1624" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1624">
+        <v>91</v>
+      </c>
+      <c r="J1624">
+        <v>5949528</v>
+      </c>
+      <c r="K1624">
+        <v>1</v>
+      </c>
+      <c r="Y1624" t="s">
+        <v>1510</v>
+      </c>
+      <c r="AB1624">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1625">
+        <v>13778</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C1625">
+        <v>3209</v>
+      </c>
+      <c r="D1625">
+        <v>30803</v>
+      </c>
+      <c r="E1625">
+        <v>8</v>
+      </c>
+      <c r="F1625">
+        <v>17</v>
+      </c>
+      <c r="G1625" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1625" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1625">
+        <v>55</v>
+      </c>
+      <c r="J1625">
+        <v>5949558</v>
+      </c>
+      <c r="K1625">
+        <v>7</v>
+      </c>
+      <c r="AC1625" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1626">
+        <v>13779</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C1626">
+        <v>6316</v>
+      </c>
+      <c r="D1626">
+        <v>61006</v>
+      </c>
+      <c r="E1626">
+        <v>4</v>
+      </c>
+      <c r="F1626">
+        <v>46</v>
+      </c>
+      <c r="G1626" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1626" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1626">
+        <v>71</v>
+      </c>
+      <c r="J1626">
+        <v>5949562</v>
+      </c>
+      <c r="K1626">
+        <v>4</v>
+      </c>
+      <c r="AB1626" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AC1626" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1627">
+        <v>13782</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C1627">
+        <v>7203</v>
+      </c>
+      <c r="D1627">
+        <v>70403</v>
+      </c>
+      <c r="E1627">
+        <v>7</v>
+      </c>
+      <c r="F1627">
+        <v>25</v>
+      </c>
+      <c r="G1627" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1627" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1627">
+        <v>74</v>
+      </c>
+      <c r="J1627">
+        <v>5949572</v>
+      </c>
+      <c r="K1627">
+        <v>2</v>
+      </c>
+      <c r="N1627">
+        <v>12</v>
+      </c>
+      <c r="AB1627">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1628">
+        <v>13783</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C1628">
+        <v>7204</v>
+      </c>
+      <c r="D1628">
+        <v>70410</v>
+      </c>
+      <c r="E1628">
+        <v>2</v>
+      </c>
+      <c r="F1628">
+        <v>36</v>
+      </c>
+      <c r="G1628" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1628" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1628">
+        <v>74</v>
+      </c>
+      <c r="J1628">
+        <v>5949576</v>
+      </c>
+      <c r="K1628">
+        <v>2</v>
+      </c>
+      <c r="AB1628">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1629">
+        <v>13785</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C1629">
+        <v>6316</v>
+      </c>
+      <c r="D1629">
+        <v>61006</v>
+      </c>
+      <c r="E1629">
+        <v>4</v>
+      </c>
+      <c r="F1629">
+        <v>47</v>
+      </c>
+      <c r="G1629" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1629" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1629">
+        <v>71</v>
+      </c>
+      <c r="J1629">
+        <v>5949584</v>
+      </c>
+      <c r="K1629">
+        <v>2</v>
+      </c>
+      <c r="AB1629" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AC1629" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1630">
+        <v>13786</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C1630">
+        <v>3613</v>
+      </c>
+      <c r="D1630">
+        <v>30608</v>
+      </c>
+      <c r="E1630">
+        <v>17</v>
+      </c>
+      <c r="F1630">
+        <v>94</v>
+      </c>
+      <c r="G1630" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1630" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1630">
+        <v>93</v>
+      </c>
+      <c r="J1630">
+        <v>5949587</v>
+      </c>
+      <c r="K1630">
+        <v>1</v>
+      </c>
+      <c r="O1630">
+        <v>21</v>
+      </c>
+      <c r="AB1630">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1631">
+        <v>13787</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C1631">
+        <v>3602</v>
+      </c>
+      <c r="D1631">
+        <v>30608</v>
+      </c>
+      <c r="E1631">
+        <v>9</v>
+      </c>
+      <c r="F1631">
+        <v>92</v>
+      </c>
+      <c r="G1631" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1631" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1631">
+        <v>93</v>
+      </c>
+      <c r="J1631">
+        <v>5949592</v>
+      </c>
+      <c r="K1631">
+        <v>3</v>
+      </c>
+      <c r="AB1631">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1632">
+        <v>13794</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1632">
+        <v>3681</v>
+      </c>
+      <c r="D1632">
+        <v>30608</v>
+      </c>
+      <c r="E1632">
+        <v>0</v>
+      </c>
+      <c r="F1632">
+        <v>85</v>
+      </c>
+      <c r="G1632" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1632" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1632">
+        <v>94</v>
+      </c>
+      <c r="J1632">
+        <v>5949624</v>
+      </c>
+      <c r="K1632">
+        <v>2</v>
+      </c>
+      <c r="Q1632" t="s">
+        <v>1523</v>
+      </c>
+      <c r="AB1632">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1633">
+        <v>13795</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C1633">
+        <v>3582</v>
+      </c>
+      <c r="D1633">
+        <v>30608</v>
+      </c>
+      <c r="E1633">
+        <v>6</v>
+      </c>
+      <c r="F1633">
+        <v>86</v>
+      </c>
+      <c r="G1633" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1633" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1633">
+        <v>94</v>
+      </c>
+      <c r="J1633">
+        <v>5949631</v>
+      </c>
+      <c r="K1633">
+        <v>3</v>
+      </c>
+      <c r="O1633" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1633">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1634">
+        <v>13800</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C1634">
+        <v>3550</v>
+      </c>
+      <c r="E1634">
+        <v>0</v>
+      </c>
+      <c r="F1634">
+        <v>47</v>
+      </c>
+      <c r="G1634" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1634">
+        <v>58</v>
+      </c>
+      <c r="J1634">
+        <v>5949646</v>
+      </c>
+      <c r="K1634">
+        <v>1</v>
+      </c>
+      <c r="W1634">
+        <v>101</v>
+      </c>
+      <c r="AB1634">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1635">
+        <v>13807</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C1635">
+        <v>3681</v>
+      </c>
+      <c r="D1635">
+        <v>30608</v>
+      </c>
+      <c r="E1635">
+        <v>6</v>
+      </c>
+      <c r="F1635">
+        <v>89</v>
+      </c>
+      <c r="G1635" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1635" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1635">
+        <v>94</v>
+      </c>
+      <c r="J1635">
+        <v>5949677</v>
+      </c>
+      <c r="K1635">
+        <v>1</v>
+      </c>
+      <c r="P1635">
+        <v>31</v>
+      </c>
+      <c r="AB1635">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1636">
+        <v>13809</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C1636">
+        <v>6410</v>
+      </c>
+      <c r="E1636">
+        <v>1</v>
+      </c>
+      <c r="F1636">
+        <v>44</v>
+      </c>
+      <c r="G1636" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1636" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1636">
+        <v>71</v>
+      </c>
+      <c r="J1636">
+        <v>5949685</v>
+      </c>
+      <c r="K1636">
+        <v>2</v>
+      </c>
+      <c r="AB1636">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1637">
+        <v>13812</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C1637">
+        <v>7308</v>
+      </c>
+      <c r="D1637">
+        <v>70605</v>
+      </c>
+      <c r="E1637">
+        <v>5</v>
+      </c>
+      <c r="F1637">
+        <v>40</v>
+      </c>
+      <c r="G1637" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1637" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1637">
+        <v>71</v>
+      </c>
+      <c r="J1637">
+        <v>5949698</v>
+      </c>
+      <c r="K1637">
+        <v>3</v>
+      </c>
+      <c r="AA1637">
+        <v>141</v>
+      </c>
+      <c r="AB1637">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1638">
+        <v>13817</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C1638">
+        <v>7408</v>
+      </c>
+      <c r="D1638">
+        <v>70605</v>
+      </c>
+      <c r="E1638">
+        <v>5</v>
+      </c>
+      <c r="F1638">
+        <v>39</v>
+      </c>
+      <c r="G1638" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1638" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1638">
+        <v>71</v>
+      </c>
+      <c r="J1638">
+        <v>5949718</v>
+      </c>
+      <c r="K1638">
+        <v>3</v>
+      </c>
+      <c r="O1638">
+        <v>21</v>
+      </c>
+      <c r="AB1638">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1639">
+        <v>13856</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C1639">
+        <v>3604</v>
+      </c>
+      <c r="E1639">
+        <v>0</v>
+      </c>
+      <c r="F1639">
+        <v>78</v>
+      </c>
+      <c r="G1639" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1639" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1639">
+        <v>91</v>
+      </c>
+      <c r="J1639">
+        <v>5949877</v>
+      </c>
+      <c r="K1639">
+        <v>1</v>
+      </c>
+      <c r="O1639">
+        <v>21</v>
+      </c>
+      <c r="AB1639">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1640">
+        <v>13937</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C1640">
+        <v>3631</v>
+      </c>
+      <c r="D1640">
+        <v>30802</v>
+      </c>
+      <c r="E1640">
+        <v>0</v>
+      </c>
+      <c r="F1640">
+        <v>29</v>
+      </c>
+      <c r="G1640" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1640" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1640">
+        <v>57</v>
+      </c>
+      <c r="J1640">
+        <v>5950224</v>
+      </c>
+      <c r="K1640">
+        <v>2</v>
+      </c>
+      <c r="O1640" t="s">
+        <v>1532</v>
+      </c>
+      <c r="AB1640">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1641">
+        <v>13940</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C1641">
+        <v>3631</v>
+      </c>
+      <c r="E1641">
+        <v>0</v>
+      </c>
+      <c r="F1641">
+        <v>32</v>
+      </c>
+      <c r="G1641" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1641" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1641">
+        <v>57</v>
+      </c>
+      <c r="J1641">
+        <v>5950232</v>
+      </c>
+      <c r="K1641">
+        <v>1</v>
+      </c>
+      <c r="O1641" t="s">
+        <v>1532</v>
+      </c>
+      <c r="AB1641">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1642">
+        <v>13959</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C1642">
+        <v>7408</v>
+      </c>
+      <c r="D1642">
+        <v>70605</v>
+      </c>
+      <c r="E1642">
+        <v>5</v>
+      </c>
+      <c r="F1642">
+        <v>46</v>
+      </c>
+      <c r="G1642" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1642" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1642">
+        <v>72</v>
+      </c>
+      <c r="J1642">
+        <v>5950313</v>
+      </c>
+      <c r="K1642">
+        <v>1</v>
+      </c>
+      <c r="O1642">
+        <v>21</v>
+      </c>
+      <c r="AB1642">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1643">
+        <v>13967</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C1643">
+        <v>6316</v>
+      </c>
+      <c r="D1643">
+        <v>61006</v>
+      </c>
+      <c r="E1643">
+        <v>4</v>
+      </c>
+      <c r="F1643">
+        <v>55</v>
+      </c>
+      <c r="G1643" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1643" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1643">
+        <v>72</v>
+      </c>
+      <c r="J1643">
+        <v>5950353</v>
+      </c>
+      <c r="K1643">
+        <v>3</v>
+      </c>
+      <c r="O1643">
+        <v>21</v>
+      </c>
+      <c r="AB1643">
+        <v>1</v>
+      </c>
+      <c r="AC1643" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1644">
+        <v>13970</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C1644">
+        <v>6416</v>
+      </c>
+      <c r="D1644">
+        <v>61006</v>
+      </c>
+      <c r="E1644">
+        <v>4</v>
+      </c>
+      <c r="F1644">
+        <v>58</v>
+      </c>
+      <c r="G1644" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1644" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1644">
+        <v>72</v>
+      </c>
+      <c r="J1644">
+        <v>5950368</v>
+      </c>
+      <c r="K1644">
+        <v>3</v>
+      </c>
+      <c r="AB1644">
+        <v>96</v>
+      </c>
+      <c r="AC1644" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1645">
+        <v>13980</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C1645">
+        <v>5601</v>
+      </c>
+      <c r="D1645">
+        <v>51106</v>
+      </c>
+      <c r="E1645">
+        <v>0</v>
+      </c>
+      <c r="F1645">
+        <v>43</v>
+      </c>
+      <c r="G1645" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1645" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1645">
+        <v>53</v>
+      </c>
+      <c r="J1645">
+        <v>5950410</v>
+      </c>
+      <c r="K1645">
+        <v>1</v>
+      </c>
+      <c r="AB1645">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1646">
+        <v>13984</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C1646">
+        <v>5601</v>
+      </c>
+      <c r="D1646">
+        <v>51106</v>
+      </c>
+      <c r="E1646">
+        <v>0</v>
+      </c>
+      <c r="F1646">
+        <v>48</v>
+      </c>
+      <c r="G1646" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1646" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1646">
+        <v>53</v>
+      </c>
+      <c r="J1646">
+        <v>5950431</v>
+      </c>
+      <c r="K1646">
+        <v>4</v>
+      </c>
+      <c r="AB1646">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1647">
+        <v>13988</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C1647">
+        <v>5511</v>
+      </c>
+      <c r="D1647">
+        <v>51106</v>
+      </c>
+      <c r="E1647">
+        <v>12</v>
+      </c>
+      <c r="F1647">
+        <v>52</v>
+      </c>
+      <c r="G1647" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1647" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1647">
+        <v>53</v>
+      </c>
+      <c r="J1647">
+        <v>5950449</v>
+      </c>
+      <c r="K1647">
+        <v>3</v>
+      </c>
+      <c r="AB1647">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1648">
+        <v>13990</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C1648">
+        <v>5611</v>
+      </c>
+      <c r="D1648">
+        <v>51106</v>
+      </c>
+      <c r="E1648">
+        <v>5</v>
+      </c>
+      <c r="F1648">
+        <v>54</v>
+      </c>
+      <c r="G1648" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1648" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1648">
+        <v>53</v>
+      </c>
+      <c r="J1648">
+        <v>5950460</v>
+      </c>
+      <c r="K1648">
+        <v>4</v>
+      </c>
+      <c r="O1648">
+        <v>21</v>
+      </c>
+      <c r="AB1648">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1649">
+        <v>13995</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C1649">
+        <v>5414</v>
+      </c>
+      <c r="D1649">
+        <v>50808</v>
+      </c>
+      <c r="E1649">
+        <v>5</v>
+      </c>
+      <c r="F1649">
+        <v>59</v>
+      </c>
+      <c r="G1649" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1649" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1649">
+        <v>53</v>
+      </c>
+      <c r="J1649">
+        <v>5950480</v>
+      </c>
+      <c r="K1649">
+        <v>2</v>
+      </c>
+      <c r="AB1649">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1650">
+        <v>14007</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1650">
+        <v>3546</v>
+      </c>
+      <c r="D1650">
+        <v>30803</v>
+      </c>
+      <c r="E1650">
+        <v>14</v>
+      </c>
+      <c r="F1650">
+        <v>36</v>
+      </c>
+      <c r="G1650" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1650" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1650">
+        <v>55</v>
+      </c>
+      <c r="J1650">
+        <v>5950534</v>
+      </c>
+      <c r="K1650">
+        <v>4</v>
+      </c>
+      <c r="AB1650">
+        <v>96</v>
+      </c>
+      <c r="AC1650" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1651">
+        <v>14021</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C1651">
+        <v>3534</v>
+      </c>
+      <c r="D1651">
+        <v>30802</v>
+      </c>
+      <c r="E1651">
+        <v>18</v>
+      </c>
+      <c r="F1651">
+        <v>28</v>
+      </c>
+      <c r="G1651" t="s">
+        <v>729</v>
+      </c>
+      <c r="H1651" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1651">
+        <v>55</v>
+      </c>
+      <c r="J1651">
+        <v>5950585</v>
+      </c>
+      <c r="K1651">
+        <v>1</v>
+      </c>
+      <c r="AB1651">
+        <v>96</v>
+      </c>
+      <c r="AC1651" t="s">
+        <v>1545</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
